--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -1,19 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INDEX" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LESSONS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MM_BOOK" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PHAN_VAI" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="INDEX" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="LESSONS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="MM_BOOK" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="PHAN_VAI" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -40,7 +39,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
@@ -62,22 +61,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00404040"/>
+        <fgColor rgb="FF404040"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
+        <fgColor rgb="FFFCE4EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,17 +90,18 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -131,7 +131,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -495,7 +495,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
@@ -504,13 +504,12 @@
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="8" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="42" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="16.8" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>FRESHWATCH CASE INDEX — hub tong: danh sach case + LESSONS + MM_BOOK + PHAN_VAI</t>
@@ -991,19 +990,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="169.5546875" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="78.21875" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="16.8" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>LESSONS LEARNED — hub bai hoc cross-case (append-only, khong xoa bai hoc cu)</t>
@@ -1053,6 +1052,11 @@
           <t>hanh_dong_tiep</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>MM</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -1532,6 +1536,524 @@
       <c r="G17" s="4" t="inlineStr">
         <is>
           <t>them cot case_id vao Zone B (viec tay 1 phut)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>L-14</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ESPORTS + twelve_cases_ref</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Wash-by-crash: crowd flush khi gia sap (long dung lo, short mo them) -&gt; gLSR tang -&gt; squeeze nguoc gia bat, short ket = nhien lieu pump. Signal: gia sap + gLSR TANG dong thoi = tiem nang squeeze nguoc (nguoc chieu voi wash-by-rally L-11)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>thesis</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>GHI NHAN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>kiem xac nhan wash-by-crash tren ESPORTS daily log khi backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>L-15</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>twelve_cases_ref + BANK/TAG</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Bait-probe: MM tao probe nho (vol spike ngan + gia retreat) do phan ung crowd. Crowd khong khang cu = san sang markup; crowd short ngay = can them wash. Probe khac markup that: khong co vol sustained sau probe</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>thesis</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>GHI NHAN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>tag probe events trong EVENTS log (BANK/TAG neu thay pattern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>L-16</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>twelve_cases_ref + BR/EVAA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>M2 dao dau (div_raw tu &gt;1 xuong &lt;1 = acc_r vuot pos_r): smart money khong con long bias hon crowd, crowd bat dau hold nhieu hon. Dao dau M2 = phase distribution bat dau. BR: div_raw 1.114-&gt;0.51 qua 10 ngay; EVAA tuong tu</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>dinh luat</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>GHI NHAN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>flag M2-flip trong DAILY log; xet lam trigger STAND_ASIDE review</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>L-17</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ESPORTS + twelve_cases_ref</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Squeeze chet khi nhien lieu chet: gLSR quay dau (gLSR_slope_5d doi dau) = short positions dong/chuyen long, het nhien lieu pump. Theo doi glsr_slope_5d: duong-&gt;am = tank can; squeeze khong the keo dai sau khi crowded-short tan</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>dinh luat</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>GHI NHAN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>them glsr_slope_5d vao S1 handover checklist</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>L-18</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>u50_verdicts §2</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>u50 §2 — Fire khong = markup ngay: can dong thoi (1) MM phase gom/markup (khong phai phan phoi), (2) crowd structure sach (gLSR hop ly), (3) OI khong PEAK. Thieu 1/3 = low-conviction, khong arm. Fire-without-phase-check dung ~40% tu 50-verdict review</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>thesis</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>GHI NHAN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>them phase_check vao ARM checklist truoc khi ARM</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>L-19</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>u50_verdicts §3</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>u50 §3 — He thong thieu phase-context filter: signal fire ban giong nhau o phase gom va phan phoi. Can phase_tag (ACCUMULATE/MARKUP/DISTRIBUTE) tu oi_cycle_pos + div_raw de loc false-fire trong phan phoi. ~30% fire trong DISTRIBUTE la false theo u50</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>GHI NHAN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>thiet ke phase_tag inference (oi_cycle_pos + div_raw + M2) — no P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>L-20</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>u50_verdicts §6 + TAG/BR 29/07</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>u50 §6 tu-ha-cap: agent ha cap confidence + ghi low_conf=True khi: fn=1, data_bad=1, missing &gt;3 ngay trong window, hoac so chot tu 1 nguon khong kiem chung duoc. So bi ha cap khong duoc lam threshold ARM/FIRE</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>DA VAO CLAUDE.md (fn=1 rule)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>mo rong tu-ha-cap cho data_bad flag (ngoai fn=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>L-21</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BR (an 30/07)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>OI daily canonical = export Binance openInterestHist 00:00 UTC. So intraday (Coinglass/GMGN) chi vao EVENTS kem timestamp, khong vao DAILY. An 30/07: BR 4,634,000 (intraday) vs 3,782,263 (export 00:00) chenh 22%. Rule: mot cot DAILY mot so canonical</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>DA VAO CLAUDE.md</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>khi co so OI: xac nhan nguon + gio chup truoc khi ghi DAILY</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>L-22</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TAG+BR 28-29/07</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>fn=1 (native_1d low_conf) khong dung lam so chot ARM/FIRE. Fallback: Zone A aggregate tu ledger_v2.xlsx CAMPAIGNS, ghi ro Zone-A-agg. TAG 29/07: gLSR 1.81 (fn=1 SUSPECT) vs 1.61 (Zone-A-agg) — chenh 0.2 du dao nhan dinh toc do nap crowd</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>DA VAO CLAUDE.md</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>khi fn&lt;6: tu dong dung Zone-A-agg + flag SUSPECT trong handover</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>L-23</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>TAG</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Fire margin mong -&gt; fade la kich ban xac suat cao: TAG 28/07 fire bien mong, ret_3d=-9.87%, crowd nap long vao duong gia xuong (gLSR 1.28-&gt;1.81). Invalidate som: gia khong confirm T+1/T+2 + gLSR tang tiep = WATCH-ha-nhiet, khong ARM lai som</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>thesis</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>GHI NHAN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>them T+1/T+2 price-confirm check vao S1 handover (48h khong confirm = WATCH-ha-nhiet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>L-24</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BR/TAG (an 30/07)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>oi_vs_med14 Excel != oi_vs_med14 signals.py (window ket thuc ngay khac). Moi so DAILY phai mang nhan: nguon + window cu the. Khong dung Excel calc lam proxy signals.py canonical. Hai nguoi doc hai so khac nhau cung ten = an tranh luan vo ich</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>DA VAO CLAUDE.md (facts da chot)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>moi oi_vs_med14 phai kem (signals.py, window=...) hoac (Excel, col X)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>L-25</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BR+TAG (tai pham 30/07)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Mot-nha-mot-data tai pham x2 trong session 30/07: (1) OI DAILY 2 so tu 2 nguon; (2) gLSR/div dung fn=1 raw thay vi aggregate canonical. Rule: moi cot DAILY mot nguon canonical khai bao tuong minh. &gt;=2 so cung metric -&gt; chon canonical + ghi an vao EVENTS</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>DA VAO CLAUDE.md (KY LUAT)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>audit cot DAILY hien tai: co cot nao 2 nguon khong khai bao khong?</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>L-26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BANK</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Backfill save nhầm file (_NEW suffix) do file gốc bị lock trong Excel — INDEX vẫn trỏ tên cũ → case_daily ghi vào file cũ (4 dòng) thay vì canonical (35 dòng). Fix: sau bất kỳ backfill nào, verify INDEX trỏ đúng canonical; canonical phải có đúng tên gốc.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>process/rule</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>GHI NHAN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>thêm bước verify file name + row count vào checklist sau backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>L-27</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BANK</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>fn=1 fallback (Zone-A-agg) chỉ dành cho cột taker_buy_pct — KHÔNG mượn sang gLSR/pos_r/acc_r. Metric ratio phải đến từ export CSV hoặc để TRỐNG + comment, không ghép chéo metric. Guard bằng assert EXPORT_COL_MAP tại import time trong case_daily.py.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>GHI NHAN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>assert đã vào case_daily.py dòng sau FORMULA_COLS</t>
         </is>
       </c>
     </row>
@@ -1547,7 +2069,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="58" customWidth="1" min="2" max="2"/>
@@ -1556,7 +2078,7 @@
     <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="16.8" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SO MM CHUNG — van tay hanh vi cross-case (chuyen tu case_tracker.md §4 ve day)</t>
@@ -1717,14 +2239,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="2" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="16.8" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>PHAN VAI LEDGER vs CASE TRACKER — duyet 30/07</t>
@@ -1739,7 +2260,7 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="7" t="inlineStr"/>
+      <c r="A4" s="7" t="n"/>
       <c r="B4" s="8" t="inlineStr">
         <is>
           <t>LEDGER v2 (so cai NGANG)</t>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -990,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1552,12 +1552,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ESPORTS + twelve_cases_ref</t>
+          <t>TAG 08-09/07 + AKE 08-10/07</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Wash-by-crash: crowd flush khi gia sap (long dung lo, short mo them) -&gt; gLSR tang -&gt; squeeze nguoc gia bat, short ket = nhien lieu pump. Signal: gia sap + gLSR TANG dong thoi = tiem nang squeeze nguoc (nguoc chieu voi wash-by-rally L-11)</t>
+          <t>Dump manh + gLSR SAP &gt;=30%/&lt;=3d = wash-by-crash: mot phat an hai: don chi phi long + nap nhien lieu short (crowd short moi = nhien lieu re cho squeeze). La bien the crowd_flush thu nhat, doi xung L-11 (rally) va L-15 (bait). Phan biet ro voi L-26: gLSR SAP khi gia sap (wash) vs gLSR TANG khi gia sap (wrong-side fuel)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GHI NHAN</t>
+          <t>DA VAO yaml (crowd_flush cause=crash)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>kiem xac nhan wash-by-crash tren ESPORTS daily log khi backfill</t>
+          <t>phan biet ro voi L-26 (gLSR TANG khi gia sap = hien tuong nguoc, KHONG phai wash)</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>twelve_cases_ref + BANK/TAG</t>
+          <t>BANK 02/07 + BASED 01&amp;09/07 + POWER 08-09/07</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bait-probe: MM tao probe nho (vol spike ngan + gia retreat) do phan ung crowd. Crowd khong khang cu = san sang markup; crowd short ngay = can them wash. Probe khac markup that: khong co vol sustained sau probe</t>
+          <t>Vol spike &gt;=8x med14 + gia bi tu choi &lt;=2d = bait-probe: muc dich khong phai markup het ma la DAY crowd short nap nhien lieu squeeze. Sau bait canh gLSR sap trong &lt;=3d lam xac nhan; vol persistence T+1 phan biet bait vs ignition that</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1604,12 +1604,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>GHI NHAN</t>
+          <t>DA VAO yaml (crowd_flush cause=bait)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>tag probe events trong EVENTS log (BANK/TAG neu thay pattern)</t>
+          <t>tag probe events trong EVENTS log khi thay pattern</t>
         </is>
       </c>
     </row>
@@ -1626,17 +1626,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>twelve_cases_ref + BR/EVAA</t>
+          <t>BR + EVAA + CLO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>M2 dao dau (div_raw tu &gt;1 xuong &lt;1 = acc_r vuot pos_r): smart money khong con long bias hon crowd, crowd bat dau hold nhieu hon. Dao dau M2 = phase distribution bat dau. BR: div_raw 1.114-&gt;0.51 qua 10 ngay; EVAA tuong tu</t>
+          <t>div_raw truot tu &gt;1 xuong &lt;1 = vi the lon thu hep/dao long bias = chom phan phoi; flag STAND_ASIDE review; khong ARM sau div-flip neu chua co bang chung re-gom. LUU Y THUAT NGU: day KHONG phai 'M2 dao dau' — M2 la module CEX balance flow (xem L-27)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>dinh luat</t>
+          <t>thesis</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>flag M2-flip trong DAILY log; xet lam trigger STAND_ASIDE review</t>
+          <t>flag div-flip trong DAILY log; ho hang gan voi lsr_dist (da la suppressor yaml)</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ESPORTS + twelve_cases_ref</t>
+          <t>AKE + ESPORTS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Squeeze chet khi nhien lieu chet: gLSR quay dau (gLSR_slope_5d doi dau) = short positions dong/chuyen long, het nhien lieu pump. Theo doi glsr_slope_5d: duong-&gt;am = tank can; squeeze khong the keo dai sau khi crowded-short tan</t>
+          <t>Squeeze/markup chet khi nhien lieu chet — hai cua dong an: (a) gLSR hoi ve ~1 (crowd short dau hang), (b) muc tieu cu the goc (TARGETED_SQUEEZE). Dang giu vi the ma mot trong hai bat = EXIT_NOW. [De xuat CHUA CALIB: thao tac hoa bang glsr_slope_5d doi dau — chua test case nao, glsr_slope_5d hien chi la cot hien thi (A5), khong phai gate]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GHI NHAN</t>
+          <t>DA VAO master plan §1 #5 + EXIT_NOW conditions</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>them glsr_slope_5d vao S1 handover checklist</t>
+          <t>neu muon slope-flip thanh trigger di duong proposal + calib nhu #17</t>
         </is>
       </c>
     </row>
@@ -1700,12 +1700,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>u50_verdicts §2</t>
+          <t>u50_verdicts §2 (n=18)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>u50 §2 — Fire khong = markup ngay: can dong thoi (1) MM phase gom/markup (khong phai phan phoi), (2) crowd structure sach (gLSR hop ly), (3) OI khong PEAK. Thieu 1/3 = low-conviction, khong arm. Fire-without-phase-check dung ~40% tu 50-verdict review</t>
+          <t>Truoc ARM phai check du 3: (1) pha chu ky (nhin du px7/px14 + oi_cycle_pos, khong chi cua so 28d), (2) crowd structure (gLSR + dao ham — co tinh gan vo dung), (3) OI khong tai PEAK. Thieu 1/3 = low-conviction. KHONG trich dan % precision khi chua do — precedent dem that (n=...), cam noi %</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>them phase_check vao ARM checklist truoc khi ARM</t>
+          <t>phase_check vao ARM checklist; precision that do bang shadow-mode P2 + alerts_log</t>
         </is>
       </c>
     </row>
@@ -1737,12 +1737,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>u50_verdicts §3</t>
+          <t>u50 §2 + CLO/BLUAI/STAR (n=18)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>u50 §3 — He thong thieu phase-context filter: signal fire ban giong nhau o phase gom va phan phoi. Can phase_tag (ACCUMULATE/MARKUP/DISTRIBUTE) tu oi_cycle_pos + div_raw de loc false-fire trong phan phoi. ~30% fire trong DISTRIBUTE la false theo u50</t>
+          <t>Signal fire ban giong nhau o pha gom va pha phan phoi — can phase_tag (ACCUMULATE/MARKUP/DISTRIBUTE/UNKNOWN) tu oi_cycle_pos + div trend + glsr_slope de loc; den khi co phase_tag: moi fire phai kem phase check tay (L-18). Khong trich % false-rate khi chua do</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1752,12 +1752,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>GHI NHAN</t>
+          <t>GHI NHAN — no P2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>thiet ke phase_tag inference (oi_cycle_pos + div_raw + M2) — no P2</t>
+          <t>thiet ke phase_tag inference trong P2</t>
         </is>
       </c>
     </row>
@@ -1774,12 +1774,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>u50_verdicts §6 + TAG/BR 29/07</t>
+          <t>TAG/BR 28-29/07</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>u50 §6 tu-ha-cap: agent ha cap confidence + ghi low_conf=True khi: fn=1, data_bad=1, missing &gt;3 ngay trong window, hoac so chot tu 1 nguon khong kiem chung duoc. So bi ha cap khong duoc lam threshold ARM/FIRE</t>
+          <t>fn=1 / data_bad=1 / missing &gt;3 ngay trong window / so tu 1 nguon khong kiem chung → low_conf=True; so bi ha cap KHONG lam threshold ARM/FIRE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1996,17 +1996,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>ESPORTS hau-climax + TAG 29/07 + BLUAI</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Backfill save nhầm file (_NEW suffix) do file gốc bị lock trong Excel — INDEX vẫn trỏ tên cũ → case_daily ghi vào file cũ (4 dòng) thay vì canonical (35 dòng). Fix: sau bất kỳ backfill nào, verify INDEX trỏ đúng canonical; canonical phải có đúng tên gốc.</t>
+          <t>Gia sap/roi + gLSR TANG = crowd long bat dao = nhien lieu SAI phia — NGUOC han wash-by-crash (L-14: gLSR SAP). He qua: (a) leg-len ke tiep can lua long nay bi rua truoc, (b) con dang SUPPRESSED co pattern nay thi REMAIN, (c) khong doc nham thanh 'co nguoi gom'</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>process/rule</t>
+          <t>thesis</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>thêm bước verify file name + row count vào checklist sau backfill</t>
+          <t>dieu kien tien quyet 'crowd flush truoc leg' ghi vao chot canh cac case dinh (TAG, BR, ESPORTS)</t>
         </is>
       </c>
     </row>
@@ -2033,27 +2033,286 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>BTW vs BAS/TAG | AKE/IDOL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>M2 (CEX balance flow) tu no KHONG mang y dinh — dau cua no do boi canh quyet: vi tri chu ky + funding regime + hanh vi gia. Chay M2 don le la An tron bay BTW. Suppressor o bat ky lop nao phu quyet moi bullish cua ca ba lop</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>dinh luat</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>DA VAO master plan §1 #1 + A1 (R4)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>giu ten 'M2' doc quyen cho balance flow — khong dung cho div/ratio (an L-16 rev.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>L-28</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>u50 §6 (AGT / HUMA-AT sync / listing 04-14)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Moi narrative dung tren mot nguon phai kiem nguon goc (aggregator != klines; mep cua so = artifact ung vien). Narrative khong con dung duoc → RUT cong khai va GHI SO muc 'da tu ha cap' — de khong tu lua va khong tai sinh. Cu luan diem chi giu phan con dung tren bang chung</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>GHI NHAN — u50 §6 la mau chuan</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>moi report lon co muc 'bang chung da tu ha cap' nhu u50</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>L-29</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>OPN + HYPER (u50 §3a, n=2)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>alpha_vol_suspect = vol_spot/vol_perp &gt; 3x → moi metric VOL SPOT cua con do ABSTAIN (khong wash-check, khong #17, khong bang chung dong tien); van dung depth/price/taker. takerBUY spot lech cuc doan (&lt;35% hoac &gt;70%) tren vol khong lo = hinh dang farming. Guard chi ha long tin, khong sinh bullish → ap ngay</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>guard</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>DA VAO amendment A6 (guard)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>cot alpha_vol_suspect vao triage/snapshot khi build spot collector (P1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>L-30</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BLUAI + ARX (u50)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Token venue_top=bitget: cam so sanh spot-vs-perp cung-ngay cho den khi bug lech ngay duoc xac minh/va; phan tich cross-market phai shift-test truoc. Ghi chu venue vao moi bang so sanh</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>data-bug</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>GHI NHAN (no ky thuat u50 #2, muc CAO)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>probe xac minh offset tren 2 token + va tai ingest</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>L-31</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>lessons_learned.md rev.1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Tong hop/dien giai tu tai lieu cu = vung rui ro cao: moi entry phai trace ve cau chu nguon (dinh nghia lay tu yaml/reference, khong tu tri nho dien giai); so lieu khong co trong nguon = khong viet; thuat ngu he thong (M1/M2/ten signal) dung dung nghia goc, khong tai dinh nghia. L-09 ap cho ca tai lieu, khong rieng fire</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>GHI NHAN</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>moi consolidation sau nay kem bang trace entry-nguon khi operator yeu cau kiem</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>L-32</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>BANK</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Backfill save nhầm file (_NEW suffix) do file gốc bị lock trong Excel — INDEX vẫn trỏ tên cũ → case_daily ghi vào file cũ (4 dòng) thay vì canonical (35 dòng). Fix: sau bất kỳ backfill nào, verify INDEX trỏ đúng canonical; canonical phải có đúng tên gốc.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>process/rule</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>GHI NHAN</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>thêm bước verify file name + row count vào checklist sau backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>L-33</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>BANK</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>fn=1 fallback (Zone-A-agg) chỉ dành cho cột taker_buy_pct — KHÔNG mượn sang gLSR/pos_r/acc_r. Metric ratio phải đến từ export CSV hoặc để TRỐNG + comment, không ghép chéo metric. Guard bằng assert EXPORT_COL_MAP tại import time trong case_daily.py.</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>rule</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>GHI NHAN</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>assert đã vào case_daily.py dòng sau FORMULA_COLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>L-34</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CASE_BANK_NEW.xlsx (an 30/07), fix da commit</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PermissionError khi save xlsx → RAISE RuntimeError ngay, cam silent-save sang ten khac (_NEW suffix). Ten file khac = INDEX tro sai = case_daily ghi nham → data bi pha vo im lang. Fix: close xlsx roi retry</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>process/rule</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>DA VAO case_daily.py (L-34 raise, commit 2026-07-30)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>backfill script cung phai RAISE neu gap lock (kiem tra backfill.py)</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -990,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2313,6 +2313,117 @@
       <c r="G38" t="inlineStr">
         <is>
           <t>backfill script cung phai RAISE neu gap lock (kiem tra backfill.py)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>L-35</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>binance-bot-signals P0 regression suite</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Bo calib (12 file _result.txt + GATE dict + replay.py) phai song trong git cung voi code — da dung, ghi nhan de giu. Quy tac: moi repo moi can regression suite commit ngay tu dau, khong de calib file ngoai version control. Loi that nhat la khi calib tach khoi code: code duoc update ma calib cu → false pass / false fail.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>process/rule</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>GHI NHAN</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>moi repo moi commit regression suite cung voi code trong 24h dau — khong phan tach calib khoi git</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>L-36</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>P0 gate session 31/07 (TAG/BTW reconstruct)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Tai tao data file phai test bang suite nguyen ban (replay.py goc tu git), KHONG tu viet harness moi. Harness tu viet dan den 3 assertion sai: (1) AKE lsr_accum: viet fires_in thay vi never_in; (2) BASED crowd_flush: viet fires_in thay vi never_in; (3) BULLA pos_rerate: dung file tai tao (pos 07-20=1.75) thay vi file goc (1.99). An: bao 40/43 gia, mat thoi gian debug. Fix: dung replay.py goc → 43/43 PASS.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>process/rule</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>GHI NHAN</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>quy trinh tai tao data: viet file → chay replay.py goc tu git → PASS truoc khi commit bat ky thu gi</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>L-37</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>B0 bundle backup 4 repo (31/07)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Repo chi local (khong remote git server) = single point of failure — mot loi o dia hay OneDrive deauth mat het. Giai phap toi thieu: git bundle → SCP len VPS /root/archive/ trong vong 24h tao repo, sau do bundle lai tai moi milestone lon. Da ap 4 repo ngay 31/07: binance-bot-signals, whale_data, Check onchain, Whales_scan. Repo OneDrive them an: file-lock + single-copy = combo sinh an (CASE_BANK_NEW, L-34).</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>DA VAO — bundle 4 repo len VPS /root/archive/ ngay 31/07</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>moi repo moi phai co bundle tren VPS trong 24h; nhac lai tai moi milestone lon</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -990,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2424,6 +2424,43 @@
       <c r="G41" t="inlineStr">
         <is>
           <t>moi repo moi phai co bundle tren VPS trong 24h; nhac lai tai moi milestone lon</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>L-38</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>BULLA 07-20 (B4 probe — 4 nguon 4 so)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Mot metric mot ngay ra 4 con so khac nhau (1.75/1.68/1.981/1.99) tu 4 nguon: (1) u50 loose = 1.75 (nguon khong ro, retired); (2) top_pos_1h keep-last 23:00 UTC = 1.6811; (3) derived_1h = 00:00 UTC dau ngay = 1.981; (4) native_1d repo goc = 1.99. Nguyen nhan: quy uoc canonical CHUA TON TAI khi calib duoc viet. He qua: verdict buoc phai chon nguon theo ket luan muon co = vi pham nguyen tac. Fix: quy uoc phai duoc ky TRUOC khi bat ky so nao duoc trich dan vao calib/DAILY. Xem proposals/ratio_daily_canonical_20260731.md cho de xuat keep-last canonical.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>GHI NHAN — proposals/ratio_daily_canonical_20260731.md cho operator ky</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ky proposals/ratio_daily_canonical_20260731.md truoc khi chay backfill tu ngay 31/07</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -990,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2461,6 +2461,43 @@
       <c r="G42" t="inlineStr">
         <is>
           <t>ky proposals/ratio_daily_canonical_20260731.md truoc khi chay backfill tu ngay 31/07</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>L-39</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>proposal v2 (31/07) — boundary canonical</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Quy ước boundary phải TEST bằng đối chiếu nguồn (21/21 diff 0%) trước khi văn bản hóa — proposal v1 hợp lý trên giấy nhưng ngược 180° với thực nghiệm; n=1 suy luận đẹp vẫn phải qua n=21.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>GHI NHAN — proposal v2 ký 31/07, CLAUDE.md updated</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>trước khi văn bản hóa quy ước metric nào: test &gt;= 21 điểm thực nghiệm đối chiếu nguồn</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -990,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2498,6 +2498,43 @@
       <c r="G43" t="inlineStr">
         <is>
           <t>trước khi văn bản hóa quy ước metric nào: test &gt;= 21 điểm thực nghiệm đối chiếu nguồn</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>L-40</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>NANSEN_KEY_LOCKED blast-radius (02/08) — bot fresh wallets</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Chốt chặn cấp máy có blast radius cấp máy — trước khi gạt công tắc dùng chung (env/key/config toàn cục), bắt buộc liệt kê MỌI consumer hợp lệ; ràng buộc nhắm vào agent phải đặt ở tầng hẹp nhất đủ dùng (per-process wrapper), không đặt tầng chung. Bằng chứng: bot fresh wallets chết 3 ngày (gap 31/07–02/08) vì NANSEN_API_KEY rename sang NANSEN_KEY_LOCKED — automated job \FreshWatch không đọc được key.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>DA SUA — run_daily_wrapper.py (02/08); FreshWatch task updated</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>trước khi rename/remove bất kỳ env/key/config toàn cục: grep MỌI consumer (scheduled task + code), sửa wrapper per-process trước khi rename</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -752,59 +752,59 @@
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>(hang cho)</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>du kien CASE-04</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>test duong concentration_shift</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>(xet)</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>hoi to, backfill tron duoc</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CASE_IDOL.xlsx</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>IDOL</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>nghi relocation / pump-staging</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>chua</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>T+7</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>cum ~5.7% supply rut Binance-&gt;vi fresh (7 vi x20M chia may) + Gate wallet +1.14%/1d, nghi relocation — operator mo an</t>
         </is>
       </c>
     </row>
@@ -816,17 +816,17 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>BTW</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>du kien CASE-05</t>
+          <t>du kien CASE-04</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>ho so trap mau</t>
+          <t>test duong concentration_shift</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -841,27 +841,27 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>MM-BAIT-B</t>
+          <t>(xet)</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>hoi to</t>
+          <t>hoi to, backfill tron duoc</t>
         </is>
       </c>
     </row>
@@ -873,17 +873,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>PARTI</t>
+          <t>BTW</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>du kien CASE-06</t>
+          <t>du kien CASE-05</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>cau truc dep gay (calib #13 NEG)</t>
+          <t>ho so trap mau</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>(xet)</t>
+          <t>MM-BAIT-B</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -930,50 +930,107 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
+          <t>PARTI</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>du kien CASE-06</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>cau truc dep gay (calib #13 NEG)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>(xet)</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>hoi to</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>(hang cho)</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
           <t>HUMA / AT</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>mo khi tell ban</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>cum van tay div~8</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>MM-BIDWALK-A?</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>leading indicator cua nhau</t>
         </is>
@@ -990,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2535,6 +2592,43 @@
       <c r="G44" t="inlineStr">
         <is>
           <t>trước khi rename/remove bất kỳ env/key/config toàn cục: grep MỌI consumer (scheduled task + code), sửa wrapper per-process trước khi rename</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>L-41</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>IDOL/TAG/BR/BANK fn=1 28-31/07 (timing bug)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Job aggregate ngay phai chay SAU khi ngay dong tron. Export mid-day = so non co he thong: tai 00:50 UTC IDOL chi co 1/6 ky funding trong store, 5 ky con lai (04:00/08:00/12:00/16:00/20:00) collect trong ngay nhung export da freeze voi fn=1. Fix: cron export 01:20 UTC D+1 (sau khi D dong + buffer 1h20); loai D khoi default_dates() range; them --force-regen de re-generate khi can.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>DA SUA — cron + script fixed 03/08; 28-31/07 re-generated</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>verify vong tu nhien: export sang 04/08 phai ra fn=6 cho ngay 03/08. Neu PASS → dong an. Quy tac: khong bao gio generate D truoc 00:05 UTC D+1.</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1073,6 +1073,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1299,6 +1300,11 @@
           <t>token dinh bai nay vao SO DEN trong MM_BOOK</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[Pham vi L-42]: Loai B/C — withdrawal gan dinh = bang chung phan phoi THAT. Loai A — withdrawal la dao cu, khong vao bang chung; chuyen sang doc theo L-42.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -1336,6 +1342,11 @@
           <t>nguong nhap: V_14d &gt;= 2x withdrawal moi coi la 'co the gom tren venue'</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[Pham vi L-42]: Ap dung khi kho xac dinh duoc Loai B hoac C. Loai A — V_venue phan xu 'mua' hay 'hang co san' khong con nghia (hang KHONG thuoc MM); chuyen sang L-42.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -1373,6 +1384,11 @@
           <t>neu BR keo that: doi chieu chot 1+2 co bao truoc khong</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>[Pham vi L-42]: Ap dung khi xac nhan Loai B/C (kho that). Loai A — kho len san = dao cu chuan bi dan, khong phai leg keo; endgame la round-trip tra no. Doc L-42 truoc L-07.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -2629,6 +2645,48 @@
       <c r="G45" t="inlineStr">
         <is>
           <t>verify vong tu nhien: export sang 04/08 phai ra fn=6 cho ngay 03/08. Neu PASS → dong an. Quy tac: khong bao gio generate D truoc 00:05 UTC D+1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>L-42</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>IDOL/TAG/BANK — kho spot MM: phan loai theo SO HUU truoc khi doc on-chain</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Kho spot cua MM khong tu no la 'hang se xa' — ham muc tieu phu thuoc SO HUU kho. Phan 3 loai TRUOC khi doc bat ky transfer nao: LOAI A (kho MUON tu team — khong gia tri voi MM; P&amp;L 100% o perp; moi deposit/withdrawal la THONG DIEP nhung nguoi doc on-chain, khong phai bang chung; endgame kho round-trip nguyen dai; dong co DAP GIA hau campaign de mua lai tra no kho — canh kho hoi day o day). LOAI B (kho unlock/dau tu — so huu that, cost thap; doanh thu phai hien thuc hoa; neo lich unlock; deposit-len-san &lt;=48h sau ngay unlock = tell hang nhat — BANK 17/07-&gt;18/07). LOAI C (tu bo tien mua tai cho — conviction that, cost basis = floor co nghia, khong deadline; loai duy nhat 'di cung thuyen' duoc). Tell phan loai: (1) NGUON kho — deployer/team wallet = nghi A; vesting contract dung lich = B; gom le nhieu nguon dai han = C; (2) nhip voi lich unlock; (3) hanh vi kho HAU DINH — round-trip nguyen = A, ban that = B; (4) do 'dien' cua transfer — chia may deu + Sent=0 trung bay = tin hieu re, nghi A. Bang chung: IDOL 3 man mot dao cu (8% vao 03-05/07 -&gt; rut 273M staging shape 13 vi -&gt; redeposit 102M) trong khi ket that o perp ~$1.2-1.8M; TAG 90B round-trip May-&gt;Jul; BANK chan unlock ban that (lai A+B); AKE 'perp vol 70x spot — spot la can gat'.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>OPERATOR KY 04/08</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>(a) cot mm_archetype{A/B/C/lai} + kho_nguon cham hoi to 12 case + case song; (b) BR kho 6% trace nguon = viec phan loai dau tien — neu team wallet -&gt; Loai A -&gt; cu flush gLSR 03/08 doc lai duoi anh sang 'dao cu man hai'; (c) moi dong PnL spot chua co sell-side xac nhan ha nhan 'unverified inference' (IDOL 111M, BANK $12-28M); (d) K3 sell-side Pancake IDOL van la test phan xu — PENDING.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Ap dung cho tat ca case co transfer on-chain. Cap nhat cho L-05/L-06/L-07: scope = Loai B/C; Loai A doc theo L-42 truoc.</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2687,6 +2687,60 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>Ap dung cho tat ca case co transfer on-chain. Cap nhat cho L-05/L-06/L-07: scope = Loai B/C; Loai A doc theo L-42 truoc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>L-44</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>L-44(a) DIEU KIEN KET THUC CAMPAIGN: Loai A (kho-muon) = ghe-roi perp la het. Loai B/C (unlock/tu-mua) = ghe-roi perp la CHUYEN PHA — ket thuc that khi kho/vol ≤10% (Cua A) hoac Cua B kich hoat (short-hedge). TUT: pos_r crash 08-05 (−48%) = GHE-ROI LAN 2 (HARVEST-INTO-STRENGTH), KHONG phai L-26, campaign van tiep tuc.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>L-45</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>L-45(b) DURATION SCALING: Thoi luong campaign ty le thuan voi build_window va kho_size. Tham khao draft n=4: BANK (build ~17d, Loai B) → campaign D+17; IDOL (build ~7d, Loai A partial) → D+11; TUT (build 13d, Loai C) → D+16+ ongoing. CLO TBD. Hypothesis: dai build = dai campaign; chua du n de calib chinh xac.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>TUT/BANK/IDOL/CLO</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,9 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="6">
@@ -107,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -129,6 +132,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -494,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -523,6 +527,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1033,6 +1038,59 @@
       <c r="K12" s="4" t="inlineStr">
         <is>
           <t>leading indicator cua nhau</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>CASE_HEI.xlsx</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>HEI</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>COLD_START — PENDING</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>cold-start perp+spot, spike events 05-29/08-05/08-06</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>COLD_START</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>duyệt operator</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="inlineStr"/>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>cold-start 08-08; contract unconfirmed; L-23 2nd depth MISSING</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1131,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -527,7 +527,15 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" s="9" t="n"/>
+      <c r="B3" s="9" t="n"/>
+      <c r="C3" s="9" t="n"/>
+      <c r="D3" s="9" t="n"/>
+      <c r="E3" s="9" t="n"/>
+      <c r="F3" s="9" t="n"/>
+      <c r="G3" s="9" t="n"/>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1091,6 +1099,47 @@
       <c r="K13" s="9" t="inlineStr">
         <is>
           <t>cold-start 08-08; contract unconfirmed; L-23 2nd depth MISSING</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>CASE_BANANAS31.xlsx</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>BANANAS31</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>COLD_START — PENDING</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Alpha fullyDelisted, dump -80% ATH, pos_r~6.7 (BTW/phan phoi?)</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>COLD_START</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr"/>
+      <c r="H14" s="9" t="inlineStr"/>
+      <c r="I14" s="9" t="inlineStr"/>
+      <c r="J14" s="9" t="inlineStr"/>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>ALPHA_21 | contract 0x3d4f...a760 BSC | cold-start 07/08/2026</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1154,7 +1154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2847,6 +2847,117 @@
       <c r="E48" t="inlineStr">
         <is>
           <t>DRAFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>L-46</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>CASE_BANANAS31 + CASE_HEI</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>Video vs Photo: hai hồ sơ pos_r cao nhưng ý nghĩa khác nhau. "Video" (CASE_HEI) = build thật: pos_r vừa phải, đồng-bộ giá, ít dist_wall. "Photo" (CASE_BANANAS31) = snapshot đẹp nhưng static: pos_r=6.7 RẤT CAO nhưng sign-corr Δpos_r vs ret_1d ~50% (47.7% opposite) — pos_r KHÔNG predict giá. Thêm: dist_wall_day=57/503 (11.3%), knife_crowd=9 ngày — dấu MM đang bán vào pump. Kết luận: pos_r level đơn độc KHÔNG phân biệt được BTW vs phân phối. Cần 3 đạo hàm: level + slope + sync. Xem Phụ lục A.5. Nguồn: CASE_BANANAS31 phân tích 08-09/08/2026 · ký 09/08 · đối chứng: CASE_HEI.xlsx</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>Khi pos_r &gt;5: check sign-corr Δpos_r vs ret_1d (30d OLS). &lt;55% → Photo → TRACKING-passive. Không vào setup cho đến đồng hồ cụm trigger (xem L-47). Implement: build_case.py đã in OLS slope + sign-corr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>L-47</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>CASE_BANANAS31</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>Đồng hồ cụm: Build-into-weakness không kéo dài vô tận. BANANAS31 pump cluster: Jun/Aug/Oct 2026 [n=3 inference từ vol spikes ≥8×med14]. Build cụm #3 từ 06/2026 → đồng hồ ~60-90 ngày → cụm #4 dự kiến Aug-Oct/26. Nếu không có ignite (gLSR≤0.7 + pos rebuild ≥3d) trong cửa sổ → build failed → MM exit. Hiện tại gLSR=1.20 &gt; ngưỡng ignite 1.1 → block entry (crowd đã long hết). Verdict NO_SETUP — TRACKING-passive. Nguồn: CASE_BANANAS31 · ký 09/08</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>Mỗi case BTW: ghi ngày dự kiến đồng hồ cụm tiếp theo. Theo dõi: gLSR drop về ≤0.7 (lý tưởng) hoặc ≤0.9 (cảnh báo). Nếu hết cửa sổ không trigger → escalate INVALIDATE check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>L-48</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>CASE_BANANAS31 + CASE_IDOL</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>fullyDelisted Alpha → ABSTAIN taker_alpha. Klines[9]==klines[5] trên BAPI khi fullyDelisted=True (taker column = close price, không phải real taker). Đã confirm: IDOL (ALPHA_223, L-43 context) + BANANAS31 (ALPHA_21). Rule chốt: IF offline=True OR offsell=True OR fullyDelisted=True → taker_alpha=NaN, flag=ABSTAIN. Áp dụng ngược cho mọi case đang mở có Alpha token. Nguồn: CASE_BANANAS31 + CASE_IDOL · ký 09/08</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>Khi collect Alpha mới: check fullyDelisted trước khi parse klines[9]. Script build_case.py đã implement ABSTAIN block. Audit retrospective: CASE_TUT/BR/CLO — check Alpha status.</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -528,13 +528,45 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="n"/>
-      <c r="B3" s="9" t="n"/>
-      <c r="C3" s="9" t="n"/>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="9" t="n"/>
-      <c r="F3" s="9" t="n"/>
-      <c r="G3" s="9" t="n"/>
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>CASE_TST.xlsx</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>TST</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>COLD_START — PENDING</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Alpha fullyDelisted, ATH=listing day, -94% drawdown. Massive vol spike 07/08 (+20%, 27x, funding negative). Cau hoi: co luc gom hang khong?</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>COLD_START</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr"/>
+      <c r="H3" s="9" t="inlineStr"/>
+      <c r="I3" s="9" t="inlineStr"/>
+      <c r="J3" s="9" t="inlineStr"/>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>ALPHA_87 | BSC 0x86bb94...666429 | cold-start 08/08/2026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1172,6 +1172,79 @@
       <c r="K14" s="9" t="inlineStr">
         <is>
           <t>ALPHA_21 | contract 0x3d4f...a760 BSC | cold-start 07/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>CASE_AGT.xlsx</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>AGT</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>COLD_START — PENDING</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Alaya Governance Token. Perp onboard 2025-05-20, ATH=2025-05-27 (0.034016). Drawdown -56%. 19 vol spikes &gt;=8x. gLSR luon &gt;1.5 (retail crowded long). GOM-A 0 fires. Cau hoi: co luc gom, dang o pha nao?</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>COLD_START</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr"/>
+      <c r="H15" s="9" t="inlineStr"/>
+      <c r="I15" s="9" t="inlineStr"/>
+      <c r="J15" s="9" t="inlineStr"/>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>ALPHA_191 | BSC 0x5dbde81...e274 | cold-start 08/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FFUSDT</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FF</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>COLD_START — AUDIT PENDING</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ALPHA_398</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bot báo gom ~$2M trên perp — tái lập số, ba phương pháp §3 độc lập</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1245,6 +1245,53 @@
       <c r="F16" t="inlineStr">
         <is>
           <t>Bot báo gom ~$2M trên perp — tái lập số, ba phương pháp §3 độc lập</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CASE_COOKIE.xlsx</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>COOKIE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>OPEN — audit-collect complete, awaiting operator verdict</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>GOM-C fire 08-03; pump pattern; ATH-97.9%; OI $1.1M</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>COLD_START</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>depth snap #2 ≥05:50 UTC</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullyDelisted=True; Q1=0(chain); oi_cycle=0.289; VWAP=$0.00774</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1292,6 +1292,51 @@
       <c r="K17" t="inlineStr">
         <is>
           <t>fullyDelisted=True; Q1=0(chain); oi_cycle=0.289; VWAP=$0.00774</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CASE_BROCCOLIF3B.xlsx</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BROCCOLIF3B</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>COLD_START</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>COLD_START</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>depth snap#2 &gt;=04:45 UTC 2026-08-10</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>BR3 audit-collect 10/08; two-broccoli confirmed distinct; DUNG cho doc</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1326,17 +1326,63 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>depth snap#2 &gt;=04:45 UTC 2026-08-10</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>BR3 audit-collect 10/08; two-broccoli confirmed distinct; DUNG cho doc</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CASE_KOMA.xlsx</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>KOMA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>GOM-C PROVISIONAL</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>COLD_START</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>depth snap#2 &gt;=05:51 UTC; GOM-C gate 15/08</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ALPHA_1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>K audit-collect 10/08; pump 07-31 +100%/$604M; OI UNCALIB; GOM-C PROV 07-23+08-02</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1368,13 +1368,11 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>depth snap#2 &gt;=05:51 UTC; GOM-C gate 15/08</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>ALPHA_1</t>
@@ -1383,6 +1381,55 @@
       <c r="K19" t="inlineStr">
         <is>
           <t>K audit-collect 10/08; pump 07-31 +100%/$604M; OI UNCALIB; GOM-C PROV 07-23+08-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CASE_APR.xlsx</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>APR</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>GOM-C 22ngay PROVISIONAL</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>COLD_START</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>depth snap#2 &gt;=07:42 UTC; GOM-C C1 gate 15/08</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>N/A (not Alpha)</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>perp-only (not Alpha); onboard 2025-10-23; ATH=$0.75→-73%; GOM-C 22d Jun-Aug; OI calib</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1415,13 +1415,11 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>depth snap#2 &gt;=07:42 UTC; GOM-C C1 gate 15/08</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>N/A (not Alpha)</t>
@@ -1430,6 +1428,38 @@
       <c r="K20" t="inlineStr">
         <is>
           <t>perp-only (not Alpha); onboard 2025-10-23; ATH=$0.75→-73%; GOM-C 22d Jun-Aug; OI calib</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CASE_BTW.xlsx</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BTW</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>COLD_START — PENDING</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>BLOWOFF2.0 echo; 3-cond trigger 0/3; OI UNCALIBRATED; GOM-C 14d pre-cool</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>WATCH (án tích refresh)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1460,6 +1460,48 @@
       <c r="F21" t="inlineStr">
         <is>
           <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CASE_ON.xlsx</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>DIST_WALL ATH-XẢ; 0 GOM-A; OI UNCALIBRATED; stage S3 xả-vùng-nhớ</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>WATCH (án mới, stage S3 pending confirmation)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>snap2 &gt;=13:02 UTC; N-4 on-chain CẦN OPERATOR</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ALPHA_444; onboard 2025-10-24; ATH $0.46 Aug7; 289 DAILY rows; contract=0x0e4f6209...</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1502,6 +1502,53 @@
       <c r="K22" t="inlineStr">
         <is>
           <t>ALPHA_444; onboard 2025-10-24; ATH $0.46 Aug7; 289 DAILY rows; contract=0x0e4f6209...</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CASE_GUA.xlsx</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>GUA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>crowd-trap; div_avg3=0.41 BEAR; gLSR=2.87 VERY BULL; 0 GOM-A; OI calib $5.4M; ATH $1.70 -97.7%; pump TODAY +54.92%</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>WATCH (án mới, pump in-progress → DỪNG chờ đọc)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>snap2 ≥15:50 UTC; G-4 on-chain CẦN OPERATOR; G-5 snap1 BID-HEAVY 1.25</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ALPHA_483</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>SUPERFORTUNE; BSC onboard 2025-12-21; ATH $1.70 May25; 231 DAILY rows; contract=0xa5c8e151...</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -1563,7 +1563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3367,6 +3367,117 @@
       <c r="G51" s="9" t="inlineStr">
         <is>
           <t>Khi collect Alpha mới: check fullyDelisted trước khi parse klines[9]. Script build_case.py đã implement ABSTAIN block. Audit retrospective: CASE_TUT/BR/CLO — check Alpha status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>L-49</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>GUARD-CÂM / ALL tokens</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>save_state() fail-open: ghi state.json không kiểm tra invariants → state corrupt không bị bắt. Sửa: validate_gom_state() wired vào save_state() pre-write (4 invariants: open chain ≤3d gap, không open+cooldown đồng thời, vwap_type hợp lệ, cooldown_end ≥ episode_start). Violation → RuntimeError → exit≠0 → Telegram alert (L-44). Commit c3d49e1.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>GUARD</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>DA VAO gom_scan.py c3d49e1</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Verify sau SCP: validator không thay đổi write behavior (md5 re-check post manual run)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>L-50</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>P0 / FFUSDT 2026-08-01</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>P0 root cause: floating-point boundary tại A3 slope_5d = 1.15. FFUSDT 08-01: slope=1.14902 (dist=0.00098 từ ngưỡng). State corrupt xảy ra vì backfill chạy lại trên đoạn đã có chapter, không phải cron viết lại. Incremental mode §8.2 đã xác nhận đúng: md5 closed-chapters IDENTICAL sau cron 01:25 UTC 08-11 (a5a929dcc4ba17f71eb3243146be2314). Vùng-rung probe: A3 có 32 changed-outcome events / 60d / 525 tokens tại ε=0.005. Mốc V4 monitor: MARGINAL-V4 đến 25/08.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>DONG — md5 PASS 11/08</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>V4 monitor: đếm chain oscillation do A2/A3 marginal qua marginal_hits.csv đến 25/08</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>L-51</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>GOM-C C1 spec / TỔNG HỢP</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Code comments (# 0.15 / # 1.5 trong signals.py) là stale defaults — không phải running values. Running values đến từ thresholds.yaml: breakout_pct=0.09 / oi_mult=1.3 (calibrated cho TUT P0-close). Spec v1.5 số đúng nhưng thiếu 3 điều kiện cấu trúc: (1) range_end=i-5 (14d range kết thúc TRƯỚC 5d build window); (2) OR-check: giá đạt target bất kỳ ngày nào trong 5d; (3) taker check là max(window)&lt;55%, không phải per-day. Bài học: khi spec nói 'X thay Y' trong changelog — luôn trace thresholds.yaml chứ không đọc code comments.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>SPEC-DRIFT</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>DE XUAT — chờ ANALYSIS ký C1 text ≤14/08</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>ANALYSIS xác nhận số canonical (0.09/1.3× hay 0.15/1.5×) + ký C1 text → operator ký ≤14/08</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -1589,6 +1589,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3462,7 +3463,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Code comments (# 0.15 / # 1.5 trong signals.py) là stale defaults — không phải running values. Running values đến từ thresholds.yaml: breakout_pct=0.09 / oi_mult=1.3 (calibrated cho TUT P0-close). Spec v1.5 số đúng nhưng thiếu 3 điều kiện cấu trúc: (1) range_end=i-5 (14d range kết thúc TRƯỚC 5d build window); (2) OR-check: giá đạt target bất kỳ ngày nào trong 5d; (3) taker check là max(window)&lt;55%, không phải per-day. Bài học: khi spec nói 'X thay Y' trong changelog — luôn trace thresholds.yaml chứ không đọc code comments.</t>
+          <t>Comment signals.py lệch yaml — comment sai (lying comments = bug), đã sửa commit 4606b86b. Running values từ thresholds.yaml: breakout_pct=0.09 / oi_mult=1.3 (calibrated TUT P0-close). Runtime-confirmed bằng _probe_c1_runtime_20260811.py STEP 1+2. Spec v1.5 '+9%/1.3×' KHỚP thresholds.yaml = ĐÚNG về số. Còn 3 điều kiện cấu trúc thiếu trong spec: (1) range_end=i-5 (14d range kết thúc TRƯỚC 5d build window); (2) OR-check: giá đạt target bất kỳ ngày nào trong 5d; (3) taker check là max(window)&lt;55%, không phải per-day. Bài học: khi spec changelog nói 'X thay Y' → luôn trace thresholds.yaml, không đọc code comments.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3472,7 +3473,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>DE XUAT — chờ ANALYSIS ký C1 text ≤14/08</t>
+          <t>DA SUA — comment fix 4606b86b + runtime-confirmed 11/08</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1549,6 +1549,43 @@
       <c r="K23" t="inlineStr">
         <is>
           <t>SUPERFORTUNE; BSC onboard 2025-12-21; ATH $1.70 May25; 231 DAILY rows; contract=0xa5c8e151...</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CASE_CYS.xlsx</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CYS</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>COLD_START — PENDING</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>GOM audit: gom thật vs staged-pump. Short squeeze Aug04-12 (+438% từ Jun trough). 4 vân: pos_r GIẢM, hedge Jul, squeeze Aug05. CẦN on-chain Solana.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>COLD_START</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ALPHA_495 | Solana | collect 13/08/2026 | on-chain CẦN OPERATOR</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1626,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1586,6 +1586,43 @@
       <c r="K24" t="inlineStr">
         <is>
           <t>ALPHA_495 | Solana | collect 13/08/2026 | on-chain CẦN OPERATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CASE_AIN.xlsx</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>AIN</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>COLD_START — PENDING</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Deposit intel: 30M token ≈ $2.4M từ 04/08. GOM-D 4/4 PASS, GOM-E PASS 29d hedge. Taxonomy BLEED. Blockchain UNKNOWN. Gate thin $78K/d. CẦN OPERATOR on-chain.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>COLD_START</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>AI narrative | chain UNKNOWN | collect 13/08/2026 | on-chain CẦN OPERATOR</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -1637,7 +1637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3552,6 +3552,33 @@
       <c r="G54" t="inlineStr">
         <is>
           <t>ANALYSIS xác nhận số canonical (0.09/1.3× hay 0.15/1.5×) + ký C1 text → operator ký ≤14/08</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>L-BUG-STALE-CASE</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CASE</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>build_case.py dùng scratch CSV theo DATE_TAG baked vào lệnh. Khi build chạy muộn (5 ngày sau fetch), data gap âm thầm — không có guard. Fix: thêm STALENESS GUARD: gap &gt; 2d → RAISE. Lesson: scratch CSV là nguồn duy nhất cho build_case; không có pipeline auto-refresh → PHẢI re-fetch trước khi build muộn.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AINUSDT 20260813 fetch, build chạy 20260817 → thiếu Aug13-16</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -923,7 +923,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>du kien CASE-05</t>
+          <t>DISTRIBUTION-WATCH</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>DISTRIBUTION-WATCH</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>COLD_START — PENDING</t>
+          <t>DISTRIBUTION-WATCH</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>DISTRIBUTION-WATCH · S2-leg3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>S2-WATCH · DISTRIBUTION</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>COLD_START — PENDING</t>
+          <t>TRACKING-ACTIVE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S25"/>
+  <dimension ref="A1:S26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1623,6 +1623,18 @@
       <c r="K25" t="inlineStr">
         <is>
           <t>AI narrative | chain UNKNOWN | collect 13/08/2026 | on-chain CẦN OPERATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TRIA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TRACKING (cold-start Aug19)</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:S27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1635,6 +1635,18 @@
       <c r="C26" t="inlineStr">
         <is>
           <t>TRACKING (cold-start Aug19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>STBL</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>TRACKING (cold-start Aug19, contract UNVERIFIED)</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S27"/>
+  <dimension ref="A1:S28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1647,6 +1647,18 @@
       <c r="C27" t="inlineStr">
         <is>
           <t>TRACKING (cold-start Aug19, contract UNVERIFIED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>HEMI</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>TRACKING (cold-start Aug20, active campaign, contract UNVERIFIED)</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S28"/>
+  <dimension ref="A1:S29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1659,6 +1659,18 @@
       <c r="C28" t="inlineStr">
         <is>
           <t>TRACKING (cold-start Aug20, active campaign, contract UNVERIFIED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PUMPBTC</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>TRACKING (cold-start Aug20, hedge episode 51d ongoing, contract VERIFIED)</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S29"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1685,7 +1685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3627,6 +3627,132 @@
       <c r="E55" t="inlineStr">
         <is>
           <t>AINUSDT 20260813 fetch, build chạy 20260817 → thiếu Aug13-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>L-52</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>TRIA + recon 4 case (BTW/GUA/APR/CLO)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Venue coverage — 'không có spot Binance' ≠ 'không có spot'. Băng thông xả và chân hàng phải tính trên venue spot LỚN NHẤT THỰC TẾ (không phải venue mặc định đầu tiên tra). Trước khi kết luận 'Alpha-only' hay 'perp-only chain': tra spot venues lớn (Bybit · OKX · Gate · KuCoin · MEXC · Bitget) trước, kết luận sau. LAYER COVERAGE mọi report case phải khai `spot-ext: &lt;venue&gt;/N/A/CHƯA-TRA` — quy ước CHƯA-TRA ≠ N/A. Cột canonical CASE schema v2.1: vol_spot_ext_usd (col 51) · spot_ext_venue (col 52) — CẤM ghi Bybit/OKX vào vol_spot_usd (col 31 = Binance api/v3 canonical). Exhibit TRIA 19/08: Bybit turnover Aug18 = $2,304,652 (3× Alpha $770K) — nếu không tra Bybit → mù nguyên một van xả 3×. Recon: GUA có Gate spot đã bỏ sót.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>VENUE</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>DA VAO — spec §D4-ext + amendment 19/08</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Case-open probe: tra ≥3 venue spot (Bybit + OKX + Gate) tối thiểu trước khi ghi verdict Alpha/perp-only. Identity-check bit-level ≥3 mẫu chống mirror trước khi dùng field mới.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>V1-20260819</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>L-53</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>CASE_HEMI (autopsy 20/08) — evidence #2 G-committed-long (BTW-July = #1)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Loài captive-kho vùng-giữa — máy perp mù theo CẤU TRÚC, không phải theo ngưỡng. Evidence HEMI 07-08/2026: 4 điểm mù cùng lúc — (1) div_avg3 vùng giữa 0.9-1.1 (pos cao 3.5 bị acc cao 3.9 che → mọi rule so-tương-đối mù) · (2) un-hedge làm 5 tuần trước ignite (episode B1 chết 09/07, ignite 15/08 — ngoài mọi cửa sổ T−2 khuôn ON và ngoài recent_hedge_days=2) · (3) vị thế long ngồi TĨNH từ trước window (không delta → mọi máy đo chuyển động câm) · (4) đòn chính = kho 490M nằm sẵn trên sàn. CẤM chỉnh A1/B1/GOM-E theo HEMI (p-hack). Hai biến thể G-committed-long: BTW div 1.3-1.5, HEMI div 0.9-1.1 + ghế tĩnh. Sensor duy trì duy nhất của loài này = on-chain kho (operator). Máy đúng tầng: PHASE-TAG bắt S3-HARVEST + TEST-BAIT real-time 18/08 — hệ nhiều tầng đúng thiết kế: tầng nền chịu mù, tầng campaign kêu.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>SPECIES</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>ACTIVE — vá bằng §E-R Un-hedge Registry v1.0</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Watch-item candidate STATIC-SEAT (PENDING n=1 HEMI, chờ đối chiếu BTW-July + fw-139 screen). Bắt bằng MỨC thay vì DELTA: pos_r ≥2.5-3 bền ≥14d ∧ OI ≤$5M ∧ funding pin ∧ kho lớn.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>H1-20260820</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>L-54</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CASE_HEMI — luật entry L-54 củng cố</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Phát hiện được ≠ giữ được lệnh. Tín hiệu sớm không có chuỗi xác nhận kế tiếp = tín hiệu không giao dịch được. Evidence HEMI: giả sử hệ HOÀN HẢO bắt cú un-hedge 05-09/07, lệnh mở tại đó phải ngồi qua 5 tuần giá đè phẳng, không tín hiệu trung gian nào (không pos_rerate, không unpin, không vol, không on-chain rút) trước ignite 15/08. Không cấu trúc xác nhận = không cấu trúc giữ = thoát trước màn hoặc gồng mù. Nguyên tắc: giá trị tín hiệu sớm = tín hiệu × chuỗi xác nhận nối được tới ignite. Tín hiệu sớm mồ côi có giá trị INTEL (registry/watchlist) chứ KHÔNG có giá trị ENTRY. Hệ quả: luật hiện hành 'entry duy nhất loài staged = S1-CONFIRMED churn ≥8×' được HEMI CỦNG CỐ chứ không bác. 'Con này không phải của mình' = kết luận đúng, có lời (tiền-không-mất), không phải thất bại hệ.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>ACTIVE — reinforces existing entry rule</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>(1) Tín hiệu sớm không kèm chuỗi xác nhận → xếp INTEL (registry/watchlist), KHÔNG mở entry. (2) Entry chỉ mở khi chuỗi xác nhận nối tới ignite proximate (≤3d default). (3) Verdict 'không phải của mình' = kết luận hợp lệ, cần thời gian ANALYSIS như positive verdict.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>H1-20260820</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -1685,7 +1685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3574,32 +3574,37 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GOM-C C1 spec / TỔNG HỢP</t>
+          <t>GUA (SUPERFORTUNE án F1-F7 19/08) + toàn hệ</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Comment signals.py lệch yaml — comment sai (lying comments = bug), đã sửa commit 4606b86b. Running values từ thresholds.yaml: breakout_pct=0.09 / oi_mult=1.3 (calibrated TUT P0-close). Runtime-confirmed bằng _probe_c1_runtime_20260811.py STEP 1+2. Spec v1.5 '+9%/1.3×' KHỚP thresholds.yaml = ĐÚNG về số. Còn 3 điều kiện cấu trúc thiếu trong spec: (1) range_end=i-5 (14d range kết thúc TRƯỚC 5d build window); (2) OR-check: giá đạt target bất kỳ ngày nào trong 5d; (3) taker check là max(window)&lt;55%, không phải per-day. Bài học: khi spec changelog nói 'X thay Y' → luôn trace thresholds.yaml, không đọc code comments.</t>
+          <t>Step-0 token-identity discipline (một-thứ-hai-tên) — trước khi dùng BẤT KỲ data từ venue nào, phải verify identity bằng 4 bước: (1) Contract canonical PHẢI từ operator-niêm (tracker-relayed 0x + chain) — cấm symbol-string lookup (bài F1 GUA: bapi trả contract khớp SUPERFORTUNE nhưng chưa đảm bảo là token operator target). (2) Bit-level compare bapi/venue contract vs operator contract (lowercase) — identical mới confirmed. (3) Price-band check: klines venue vs klines perp ±20% (tolerance rộng cho illiquid Alpha). Ngoài band = FALSE-VENUE. (4) Van flag deposit/withdraw per chain — LOCKED chain = ISOLATED, không đếm băng-thông xả. Bằng chứng F1-F7: bapi ALPHA_483 SUPERFORTUNE contract 0xa5c8e15... — CẦN operator 0x mới quyết True/False venue. Áp dụng: TRIA (Bybit), STBL (Gate+MEXC+KuCoin+Alpha), HEMI (Gate+MEXC, Alpha delisted), PUMPBTC (MEXC+Gate+Bitget, verified 20/08). Old L-51 content (GOM-C C1 spec drift 11/08) archived in git history — canonical L-51 từ nay = Step-0 identity discipline.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SPEC-DRIFT</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>DA SUA — comment fix 4606b86b + runtime-confirmed 11/08</t>
+          <t>DA VAO — spec + code hoá bắt buộc (đang chờ collector Step-0 assert)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>ANALYSIS xác nhận số canonical (0.09/1.3× hay 0.15/1.5×) + ký C1 text → operator ký ≤14/08</t>
+          <t>Case-open mọi token mới: Step-0 (contract canonical operator) TRƯỚC data load. Collector code: add contract_canonical field + assert bit-eq trước fetch/store. Amendment cho tất cả CASE files: cột `contract_canonical` (row 7 CASE meta). Ref: docs/reports/_gua_identity_forensics_20260819.md §F6 schema v2.1-ext</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>F1-20260819</t>
         </is>
       </c>
     </row>
@@ -3753,6 +3758,48 @@
       <c r="H58" t="inlineStr">
         <is>
           <t>H1-20260820</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>L-48-AMD</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Amendment L-48 (ref L-48 fullyDelisted) — token Alpha-only cross fw-139 × Binance spot</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Amendment L-48 (19/08) NGUYÊN VĂN operator: 'phạm vi mở rộng — token Alpha-only (danh sách N token theo probe cross exchangeInfo 18/08): taker_spot_pct và taker_alpha = ABSTAIN-STRUCTURAL (không phải data-gap) · vol_spot_usd = N/A-STRUCTURAL · số Alpha chỉ ở vol_alpha.' N COUNT (nợ 18/08, trả 21/08 probe _probe_alpha_only_N_20260821): N = 88 tokens Alpha-only / fw-139 tổng 139 tokens (51 có Binance spot pair). Danh sách 88 token snapshot 21/08: scratch/alpha_only_fw139_20260821.csv. Bao gồm các case đang mở: AGT, AIN, APR, BR, BTW, CLO, CYS, GUA, HEMI, IDOL, KOMA, ON, PUMPBTC, STBL, TAG, TRIA, XPIN (17/17 case active KHÔNG có Binance spot pair — toàn Alpha-only).</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AMENDMENT</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>DA VAO — 21/08 (nguyên văn operator + N count trả nợ)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Mọi case Alpha-only từ nay MẶC ĐỊNH tag: vol_spot_usd=N/A-STRUCTURAL · taker_spot_pct/taker_alpha=ABSTAIN-STRUCTURAL · vol chỉ điền vol_alpha (col 35). Universe cross-check chạy lại khi Binance list token mới (delta 51→N reassess). Ref: probe scratch/alpha_only_fw139_20260821.csv, canonical N snapshot 21/08.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>AMEND-L48-20260819</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -1685,7 +1685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Case-open mọi token mới: Step-0 (contract canonical operator) TRƯỚC data load. Collector code: add contract_canonical field + assert bit-eq trước fetch/store. Amendment cho tất cả CASE files: cột `contract_canonical` (row 7 CASE meta). Ref: docs/reports/_gua_identity_forensics_20260819.md §F6 schema v2.1-ext</t>
+          <t>Case-open mọi token mới: Step-0 (contract canonical operator) TRƯỚC data load. Collector code: add contract_canonical field + assert bit-eq trước fetch/store. Amendment cho tất cả CASE files: cột `contract_canonical` (row 7 CASE meta). Ref: docs/reports/_gua_identity_forensics_20260819.md §F6 schema v2.1-ext · ARCHIVE-REF: old L-51 content (GOM-C C1 spec drift 11/08, commit 49f1cd6 và trước) archived in git history — canonical L-51 từ nay = Step-0 identity discipline.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3800,6 +3800,300 @@
       <c r="H59" t="inlineStr">
         <is>
           <t>AMEND-L48-20260819</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>L-60</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>án E LSR-merge (GUA rebuild 17/08) — schema mismatch silent</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>SCHEMA-DRIFT-CÂM: schema mismatch giữa producer + consumer = corrupt SILENT (không alert, hệ tin data đúng nhưng đọc sai). Evidence án E LSR-merge autopsy 17/08 (docs/reports/_probe_lsr_merge_20260817.md): fetch script `_probe_gua_apr_rebuild_20260817.py` fetch_lsr() viết CSV với schema Binance raw (`longShortRatio/longAccount/shortAccount`); build_case.py A-0a chỉ nhận `pos_r_raw|pos_r`, `acc_r_raw|acc_r`, `glsr_raw|gLSR|glsr` — schema mismatch → tất cả 30 dates Jul19-Aug17 vào `lsr_by_d` với all-None values, freshwatch loop skip vì dates đã occupied → CASE_GUA.xlsx corrupted (pos_r null 100%). Rule chốt: (1) mọi CSV producer khai schema explicitly ở header + provenance metadata; (2) mọi consumer assert schema-check TRƯỚC compute — mismatch = RAISE + block, không silent None; (3) fetch scripts + consumers cùng amendment cùng chuyến khi schema đổi. Ghi chú: renumbered from V1 draft-49 — va số với chủ cũ L-49 (11/08 GUARD-CÂM state.json), phát hiện 21/08 audit. Nguồn text: proposals/lessons_pending_batch_20260818.md §C.* context + án E report + chat-ký 21/08 operator.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>SCHEMA</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>DA VAO — 21/08 (renumbered from V1 draft-49)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Proposal Fix áp cho build_case.py A-0a: schema-check assert + Fix B nguồn (sửa fetch_lsr() output canonical schema). Ref: án E report §4-§5 fix proposals A/B/C.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>V1-renum-20260821</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>L-61</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>án E LSR-merge (GUA rebuild 17/08) — XLSX ghi trước guard check</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>WRITE-BEFORE-GUARD anti-pattern (fix = WRITE-AFTER-GUARD): mọi write persistent (xlsx save, csv commit, DB write) PHẢI SAU khi ALL guards pass — write TRƯỚC guard = corrupt state on-disk khi guard fail. Evidence án E: build_case.py XLSX write ~line 800-856 (wb.save()) TRƯỚC A-0b guard check line 857-868. Khi A-0b raise ValueError (pos_r null &gt; 50%) → exit≠0 nhưng XLSX đã corrupted trên disk (GUA 100% null, APR 75%). Guard fires DID fire correctly (đúng logic), nhưng vô nghĩa vì corrupted state đã persist. Rule chốt: (1) build dataframe fully in-memory; (2) run ALL guards on in-memory df; (3) write to disk CHỈ SAU guards pass; (4) guard fail = discard in-memory + exit không đụng disk. Áp dụng: đã tuân thủ trong GUA refresh 18/08 + TRIA venue backfill 19/08 + STBL/HEMI/PUMPBTC create 19-20/08. Ghi chú: renumbered from V1 draft-50 — va số với chủ cũ L-50 (11/08 FFUSDT P0), phát hiện 21/08 audit. Nguồn text: proposals/lessons_pending_batch_20260818.md §C.* + án E fix proposals + chat-ký 21/08 operator.</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>WRITE-GUARD</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>DA VAO — 21/08 (renumbered from V1 draft-50)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Refactor build_case.py: move all guards trước wb.save(). Same rule for any script producing xlsx/csv/db writes. Verification: mọi task từ 18/08+ đã tuân thủ write-after-guard.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>V1-renum-20260821</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>L-55</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>PHASE-TAG go-live 20/08 · save_snapshot fail-câm · 🎓 badge</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>GO-LIVE ≠ VERIFY: deploy xong chưa phải xong — go-live chỉ ĐÓNG khi verify OUTPUT THẬT trên production (file sinh · đúng schema · đúng giờ cron). Evidence: phase_tag CSV F1 code-đúng-file-không-sinh 3 ngày · save_snapshot fail-câm · 🎓 (badge graduation) sống lần đầu chỉ sau verify 20/08. Rule: mọi go-live commit phải kèm verify checklist (output artifact + schema + timing + integration). Signed batch V2 · operator ký chat 21/08.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>GO-LIVE</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>DA VAO — batch V2 21/08</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Go-live commit template: paste verify output artifact + schema + timing + integration test result.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>V2-20260821</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>L-56</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>6 relay-loss/tuần (L-48 số hiệu · GUA contract · E-R4b ≥-drift · handover · lib · va số 49/50)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>MERGE-BEFORE-GATE: amendment ký chat PHẢI merge canonical + paste diff TRƯỚC gate/backfill run. Mọi run gate in `spec_version` + `amendments_applied`. Dòng 'ĐÃ KÝ' trong sổ PHẢI trỏ được về chat-ký commit/URL — không trỏ được = CHỜ-KÝ. Evidence 6 relay-loss/tuần 15-21/08: (1) L-48 số hiệu drift · (2) GUA contract chưa relay verified · (3) E-R4b ≥1.15 vs &lt;1.15 drift · (4) handover ký-không-tồn-tại · (5) lib đổi-nghĩa silent · (6) va số L-49/L-50 chủ cũ vs V1 batch (P3 audit 21/08). Signed batch V2 · operator ký chat 21/08.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>GATE-DISCIPLINE</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>DA VAO — batch V2 21/08</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Gate/backfill runner: mandatory print(spec_version, amendments_applied). Commit template chat-ký link required.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>V2-20260821</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>L-57</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Schema evolution (cols 51-52 v2.1 · ep_len/struct_n · vol_spot/vol_alpha)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>SCHEMA-CHANGE-APPEND: thay đổi schema = APPEND-ONLY + changelog + KHÔNG đè cột cũ. Cột đổi NGHĨA phải ĐỔI TÊN (không giữ tên cũ mang nghĩa mới — bài F1 'một-thứ-hai-tên'). Evidence: (1) cols 51-52 v2.1 spot-ext amendment (append canonical, không đè col 31); (2) ep_len vs struct_n (2 tên cho 2 nghĩa khác nhau — không alias); (3) vol_spot vs vol_alpha (col 31 vs col 35, không mix). Signed batch V2 · operator ký chat 21/08.</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>SCHEMA-EVOLUTION</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>DA VAO — batch V2 21/08</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>PR review checklist: schema change = append-only? changelog? tên cột đúng nghĩa mới? Nếu có drift → block merge.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>V2-20260821</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>L-58</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>E-R7d/e drift incidents + P0 CHECK watchlist inline vs lib (2ba669f)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CONFORMANCE FIXTURE: pin output MỌI consumer, không-pass-không-merge, đổi ngữ nghĩa = amendment ký riêng, fixture chạy trong mọi gate run. Mỗi consumer (watchlist · registry · phase_tag · gom_scan · downstream analyzers) có fixture file (`tests/fixtures/&lt;consumer&gt;_conformance_&lt;YYYYMMDD&gt;.json`) pin OUTPUT actual (events/episodes/labels/metric values) trên data snapshot cụ thể (freshwatch csv với md5 lock). CI/pre-commit hook check fixture — commit đụng consumer path mà fixture FAIL → block merge. Không exception. Đổi ngữ nghĩa = ký amendment spec + regen fixture + update cùng commit + bump version. Fixture chạy TRƯỚC compute trong mọi gate/backfill — mismatch = STOP. Signed batch V2 · operator ký chat 21/08. Ref: proposals/lessons_pending_batch_V2.md §A.1.</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>CONFORMANCE</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>DA VAO — batch V2 21/08 (fixture chưa build)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Kickoff phase-2: build fixture files 5 tokens (HEMI/ON/GUA/CARV/ARIA) cho registry+watchlist+phase_tag. Add pre-commit hook + CI script trước phase-2 cron 08:25.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>V2-20260821</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>L-59</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Batch V1 20/08 · P0 audit 21/08 (root-cause 'hiểu-nhầm-nhà')</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>KÝ-KHÔNG-BẰNG-CHỨNG = CHƯA-XONG: lệnh ghi-sổ đã ký ĐÓNG bằng paste bằng-chứng-sau-ghi CÙNG chuyến. Không bằng chứng = việc CHƯA TỒN TẠI, CHẶN bước phụ thuộc. Sổ hai nhà (nguồn + view) khai rõ nguồn/view; view CHẾT &gt;3d khi nguồn SỐNG = ALERT. Evidence #1: batch V1 ký 20/08 — 3 lần đòi không có bằng chứng (L-52/53/54 vào pending_batch nhưng chưa sync sheet), operator tự phát hiện md lessons_learned CHẾT từ 07/08 (14 ngày stale) trong khi sheet đã append đợt sau. Evidence #2: root-cause 'hiểu-nhầm-nhà' 21/08 P3 audit (agent commit pending_batch chờ operator paste tay, operator ký = agent nhập ngay + regen view). Signed batch V2 · operator ký chat 21/08.</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>GOVERNANCE</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>DA VAO — batch V2 21/08</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Mọi commit ký lesson/spec/amendment: mandatory paste bằng-chứng-sau-ghi (mtime · sheet row · md section · commit sha). Cron alert: staleness check view vs nguồn — view/md mtime lag &gt; 3d = Telegram alert.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>V2-20260821</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:S30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1671,6 +1671,18 @@
       <c r="C29" t="inlineStr">
         <is>
           <t>TRACKING (cold-start Aug20, hedge episode 51d ongoing, contract VERIFIED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>AKE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>COLD_START 21/08 (R2 nhịp 1) — DAILY populated, contract UNVERIFIED (nhịp 2)</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S30"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1686,6 +1686,28 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CAP</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>COLD_START</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>23/08 fresh operator paste contract</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1697,7 +1719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1715,6 +1737,11 @@
           <t>LESSONS LEARNED — hub bai hoc cross-case (append-only, khong xoa bai hoc cu)</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>amendment</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -3688,6 +3715,11 @@
           <t>V1-20260819</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>AMENDMENT 21/08/2026: MEXC không được làm venue chính cho cols 51-52 (vol thường ảo). Sweep vẫn liệt kê MEXC, xếp hạng chọn venue loại MEXC ra; MEXC là #1 → lấy #2. MEXC trong spot_ext_venue = 'THÔNG/VOL-UNTRUSTED' cho doctrine #10 (băng thông = venue #2). Áp hồi tố mọi CASE có spot_ext_venue=mexc (BANK 21/08 confirmed). Ref: playbook §IX.3 S0.④ AMENDMENT. || AMENDMENT (b) 21/08/2026: Venue chính cols 51-52 xếp theo MEDIAN vol toàn window (hoặc theo pha nếu sàn dẫn đổi giữa window), KHÔNG theo 24h snapshot. MEXC loại theo (a). Sàn dẫn đổi giữa window → ghi venue_switch + ngày vào CASE meta, cols 51-52 ghi venue đúng từng ngày. Nếu §6 phase file chưa có → dùng median toàn window làm winner default. Ref: playbook §IX.3 S0.④ AMENDMENT (b).</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4106,6 +4138,154 @@
       <c r="H66" t="inlineStr">
         <is>
           <t>V2-20260821</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>L-62</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ERRATA-BAND-20260827 (⑬-CLOSE probe 5b + Scope-A hardcode band mismatch)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Đường-đọc-thật: số/nhãn/verdict do probe/gate xuất ra CHỈ hợp lệ khi declare đường-đọc-thật của mọi ngưỡng dùng trong tính toán. Không declare = thước tách khỏi số = bảng vô hiệu. Rule bắt buộc header cfg-provenance: Nguồn thresholds (yaml path | hardcode | free-layer) + Giá trị THỰC từng ngưỡng dùng (không dựa comment) + Timestamp yaml mtime nếu source = yaml (staleness detect). Evidence: ERRATA-BAND-20260827 d353dc4 probe hardcode 0.505 vs prod 53.0.</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>RULE-DISCIPLINE</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>SIGNED batch V3 27/08 → sheet 67</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Rà lại hardcode probe/task; thay yaml load + provenance header. Pre-commit hook 'no hardcoded thresholds' pending scope ký.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>L-63</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>⑩-AMENDMENT chuỗi 24-26/08 (⑩ stub → 3 vế mở rộng, R4-v2 avg_px scope-miss)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>SCOPE-BY-MANIFEST: scope regen/canonicalize/migrate định nghĩa bằng DANH SÁCH BIẾN CANONICAL BỊ ẢNH HƯỞNG (fields cụ thể: taker_buy_pct, avg_px, lsr_pos, ...) và block chứa nó (KLINES/RATIO/OI), KHÔNG bằng tên slice mờ ('taker slice', 'LSR slice'). Manifest bảng per (block, col, source, consumer, canonical, verdict) làm nguồn duy nhất; xung đột → CONFLICT column, DỪNG hỏi. Evidence: ⑩ initial stub → R4-v1 chạm RATIO taker → B3 fail hội tụ do avg_px (KLINES) chưa regen → R4-v2 mở rộng scope. Manifest v1 SIGNED 4cd6ec3.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>SCOPE-DISCIPLINE</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>SIGNED batch V3 27/08 → sheet 68</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Mọi ⑥ regen/⑩ migrate/canonicalize ⇒ manifest bảng trước; verdict per col: REGEN / VERIFY-THEN-KEEP / DEPRECATE-RENAME / N/A-BLOCK. Missing col = CONFLICT DỪNG.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>L-64</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ERRATA-BAND-20260827 fix 2 probe hardcode</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>cfg-provenance header: mọi probe/gate BẮT BUỘC in header cfg-provenance tại đầu run: [CFG-PROVENANCE &lt;artifact&gt;] Source: &lt;yaml path | hardcode | free-layer&gt; · Method: &lt;load method&gt; · Values ACTUALLY USED: &lt;threshold_name&gt; = &lt;actual_value&gt; [comment: source line]. Kèm assertions fail-loud khi mismatch. Không header = bảng vô hiệu (L-62 companion). Evidence: ERRATA-BAND d353dc4 fix _probe_5b_consumer_diff + _task_backfill_apply.</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>PROBE-DISCIPLINE</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>SIGNED batch V3 27/08 → sheet 69</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Template header in gom_scan.load_thresholds() wrapper; probe/task print auto. Lint rule pending scope ký.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>L-65</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ERRATA-BAND-20260827 subset check FAIL 8+27 extras + ARIA/STAR spot</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Flip-set XOR hai chiều (band-change không đơn điệu): rule cũ 'band nới chỉ bớt flip' = GIẢ ĐỊNH SAI (L-28 DEV-instance). Rule ĐÚNG: flip-set dưới band-change là XOR HAI CHIỀU — mọi thay đổi band ⇒ RERUN toàn bộ bằng chứng flip, subset không được giả định. Mechanism: wider band = more 7d-window all-pass cases → flip transition NEW cases không tồn tại narrow band. Evidence: ERRATA subset FAIL (5b 8 extras, Scope-A 27 extras); ARIA 07-30 canonical crosses 0.53 boundary; STAR 06-28 canonical 06-24=0.5304 &gt; 0.53 → PROD flip leg=T can=F. Documentation phải note 'subset không được giả định' cạnh mọi flip-count report.</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RULE-CORRECTION</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>SIGNED batch V3 27/08 → sheet 70</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>R6 skeleton vocabulary + E2-backlog note updated. Mọi flip-report post-⑬ dùng rule mới.</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1708,6 +1708,28 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BTR</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>COLD_START-WATCHLIST-REPLAY</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>23/08 cold start + watchlist diagnostic. Contract UNVERIFIED.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1719,7 +1741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1750,6 +1772,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3717,7 +3740,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>AMENDMENT 21/08/2026: MEXC không được làm venue chính cho cols 51-52 (vol thường ảo). Sweep vẫn liệt kê MEXC, xếp hạng chọn venue loại MEXC ra; MEXC là #1 → lấy #2. MEXC trong spot_ext_venue = 'THÔNG/VOL-UNTRUSTED' cho doctrine #10 (băng thông = venue #2). Áp hồi tố mọi CASE có spot_ext_venue=mexc (BANK 21/08 confirmed). Ref: playbook §IX.3 S0.④ AMENDMENT. || AMENDMENT (b) 21/08/2026: Venue chính cols 51-52 xếp theo MEDIAN vol toàn window (hoặc theo pha nếu sàn dẫn đổi giữa window), KHÔNG theo 24h snapshot. MEXC loại theo (a). Sàn dẫn đổi giữa window → ghi venue_switch + ngày vào CASE meta, cols 51-52 ghi venue đúng từng ngày. Nếu §6 phase file chưa có → dùng median toàn window làm winner default. Ref: playbook §IX.3 S0.④ AMENDMENT (b).</t>
+          <t>AMENDMENT 21/08/2026: MEXC không được làm venue chính cho cols 51-52 (vol thường ảo). Sweep vẫn liệt kê MEXC, xếp hạng chọn venue loại MEXC ra; MEXC là #1 → lấy #2. MEXC trong spot_ext_venue = 'THÔNG/VOL-UNTRUSTED' cho doctrine #10 (băng thông = venue #2). Áp hồi tố mọi CASE có spot_ext_venue=mexc (BANK 21/08 confirmed). Ref: playbook §IX.3 S0.④ AMENDMENT. || AMENDMENT (b) 21/08/2026: Venue chính cols 51-52 xếp theo MEDIAN vol toàn window (hoặc theo pha nếu sàn dẫn đổi giữa window), KHÔNG theo 24h snapshot. MEXC loại theo (a). Sàn dẫn đổi giữa window → ghi venue_switch + ngày vào CASE meta, cols 51-52 ghi venue đúng từng ngày. Nếu §6 phase file chưa có → dùng median toàn window làm winner default. Ref: playbook §IX.3 S0.④ AMENDMENT (b). || AMENDMENT (c) 27/08/2026: Vũ trụ sweep venue BẮT BUỘC gồm Binance spot, kiểm theo-con qua spot exchangeInfo. ALPHA-DELISTED ⇒ check spot-listing là bước bắt buộc (delist thường = tốt nghiệp lên spot). Binance spot nếu có tham gia xếp hạng median L-52(b) như mọi venue — và là nguồn taker spot canonical khi thắng (k[10]/k[7], basis ⑩). Ref: playbook §IX.3 S0.④ AMENDMENT (c).</t>
         </is>
       </c>
     </row>
@@ -4286,6 +4309,997 @@
       <c r="G70" t="inlineStr">
         <is>
           <t>R6 skeleton vocabulary + E2-backlog note updated. Mọi flip-report post-⑬ dùng rule mới.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>L-66</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>batch_lessons_202609 (md5=28fe5a43) · A1 · SILENT-FAIL FAMILY</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>L-66 SILENT-FAIL FAMILY (hợp nhất + taxonomy B1-B4): Cấm `except: pass` trần trên mọi đường tính signal/alert. Mọi exception nuốt phải phát sentinel `N/A-ERROR:&lt;tên&gt;` vào output — máy được phép hỏng, không được phép hỏng câm. Sentinel áp cả provenance-fields (header/md5/version-string), không chỉ signal-values. Taxonomy dạng câm: B1 exit-0-rỗng · B2 exit-dối-mtime-cũ · B3 except-swallow-print-hư-vô · B4 error-printer-tự-chết. Hai luật máy: M1 mtime là bằng chứng exit-code không phải · M2 máy báo lỗi không được phép tự chết. Import-prod chỉ đúng khi prod pass conformance fixture ghim spec tại sha đang import. Ba-tầng-vá kết dính B2-mtime · B3/B4-stderr · L-51-getter-fail-loud → STALE-SENT cần BA lá cờ cùng đen (defense-in-depth). Án lệ: save_snapshot · BTR detect-vs-wire · ramp-4-revs · auto-untrip · header-compose · probe-V③ · vụ Nansen-migration B1-B4 (31/08).</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>SILENT-FAIL-FAMILY</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>DA VAO</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>grep-lint pre-merge · enforcement via pre-commit hook getenv-sweep + except:pass detector</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>L-67</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>batch_lessons_202609 (md5=28fe5a43) · A2 · FIXTURE-IMMUTABILITY</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>L-67 FIXTURE-IMMUTABILITY: Pin/expected của fixture là VĂN BẢN KÝ — chỉ operator được thêm/bớt/sửa qua amendment có diff. Agent/DEV tự đổi pin/bỏ row/viết điều kiện mới né ca đang fail = **vi phạm loại-1** (ngang tự-ký verdict): mọi 'PASS' sinh sau vô hiệu toàn bộ. Enforcement máy: (a) fixture file mang md5 niêm trong spec · runner in `fixture_md5` mỗi run · lệch = FAIL-toàn-bộ tự động; (b) 'n/n PASS' chỉ có nghĩa khi kèm fixture_md5 khớp bản niêm. Lesson viết theo hệ quả không theo ý định. Án lệ: preview-2 render-v2 (pin-swap F1/TAC/HUMA + p8 né-BTR) — biến thể '8/8 PASS ≠ pass'. Addendum semantics-đếm: ngày-nén n = target_date − fire_date (fire-day=0) — định nghĩa trích từ sổ đang chạy, không từ trực giác; pin p9 anchor kép MIRA+ERA giữ vĩnh viễn.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>FIXTURE-IMMUTABILITY</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>DA VAO</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>fixture_md5 print mỗi run · pins LOCKED file (docs/proposals/render_v2_fixture_pins_LOCKED.md) rev2 md5=23500dc7</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>L-51-AMD-BRIDGE</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>batch_lessons_202609 (md5=28fe5a43) · A3 · BRIDGE-INJECT hai-đường-chạy · Nansen 31/08</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>L-51 amendment BRIDGE-INJECT hai-đường-chạy (bản-rev · bless từ evidence 31/08): Định danh dùng chung phải có MỘT getter · mọi đường (cron/manual/probe/one-off/emergency-run) qua CÙNG cửa. Đường không-cầu = hai-nguồn-sự-thật runtime · SILENT cho tới khi bỏ cầu. Án lệ: Nansen key-migration 09/2026 — cron path đi qua wrapper inject `NANSEN_API_KEY = NANSEN_KEY_LOCKED` cho subprocess child → work; manual `python run_daily.py` bỏ qua wrapper → key empty → silent-swallow B3 → STALE-SENT. Enforcement: single-getter (ví dụ `core_nansen.get_api_key()`) reads canonical name first + fallback deprecated + DeprecationWarning; pre-commit hook grep dangling `os.getenv("&lt;KEY&gt;")` outside getter → fail. Họ L-51: bridge-inject giữ hai-đường-chạy sống dai · cause thật lộ khi bỏ cầu — không phải 'rename quét thiếu'; git blame chứng minh line-đọc-key không bị đổi trong khoảng gây bug.</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>IDENTITY-AMENDMENT</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>DA VAO</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>core_nansen.get_api_key() vá 31/08 · lesson_L51_bridge_inject_L66_B3B4_20260831.md · pre-commit hook getenv-sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>L-68</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>batch_lessons_202609 (md5=28fe5a43) · A4 · SIGNATURE-FROM-CANONICAL · án lệ A10-RERATE</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>L-68 SIGNATURE-FROM-CANONICAL: Mọi rule mới trình ký phải kèm bảng số evidence-case tính TỪ FILE CANONICAL bằng ĐÚNG công thức operationalization — fixture-check TRƯỚC chữ ký, không phải sau. Án lệ: A10-RERATE (ngưỡng đặt từ đọc-mắt ảnh UI, chết ngay lượt fixture-prep).</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>SIGNATURE-DISCIPLINE</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>DA VAO</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>fixture-check bắt buộc trước ký · playbook §</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>L-69</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>batch_lessons_202609 (md5=28fe5a43) · A5 · AMENDMENT-VERBATIM · án lệ A/B khối-🌊</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>L-69 AMENDMENT-VERBATIM / CHỮ-CÁI-RETIRED: Amendment/ruling relay mang NỘI DUNG nguyên văn, không mang con trỏ (A/B, option-1/2) — nhãn tham chiếu chết khi rời ngữ cảnh sinh ra nó. Án lệ: suýt-đảo A/B khối-🌊 (agent tự dựng bảng ngược chiều). Bổ trợ luật cũ 'request verbatim text, do not reconstruct mechanism'.</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AMENDMENT-DISCIPLINE</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>DA VAO</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>amendment relay verbatim · chữ-cái retired</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>L-70</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>batch_lessons_202609 (md5=28fe5a43) · A6 · EXPECTED-TARGET-DATE · án lệ suýt-chấm-nhầm-đêm</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>L-70 EXPECTED-TARGET-DATE (enforcement lắp cùng batch): Mọi bảng expected của dao-trôi/verify phải mang cột `target_date`; runner đối chiếu `target_date ≡ render_date` TRƯỚC khi so giá trị — lệch = FAIL-ENGINE, không vào so số. Án lệ: expected 08-30 suýt chấm đêm 08-31. Họ fixture_md5: trọng tài phải tự khai nó đang chấm đêm nào.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>EXPECTED-TARGET-DISCIPLINE</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>DA VAO</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>pins rev3 target_date column + fixture rev3 _assert_target FAIL-ENGINE (apply cùng batch 31/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>L-71</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>batch_lessons_202609 (md5=28fe5a43) · A7 · BỘ LUẬT ĐỌC-BẢNG hợp nhất</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>L-71 BỘ LUẬT ĐỌC-BẢNG (niêm gộp): (1) Vùng-dao: chữ ký tham số chỉ có giá trị trong vùng dao nó sẽ sống; thắng-thua ngoài vùng in kèm trung thực, không tham gia verdict. (2) ±MC: điểm-ước-lượng từ bootstrap/MC phải khai phương-sai-máy-đo; số chưa kèm ±MC chưa phải số ký; claim vắt ranh bắt buộc re-draw độc lập. (3) Pool = regime-leg: control-pool của một nhãn phải mirror đúng regime-leg của chính nhãn (trừ pass-set); all-days là confound. (4) So-sánh-cùng-thước: mọi cặp số verdict phải cùng đơn vị/cùng luật cụm/cùng censor — unit-mismatch, length-mismatch là án tự hủy bảng. (5) Probe-pass-fixture-first: mọi bảng probe/counterfactual phải PASS fixture-trọng-tài trước khi ANALYSIS chấm số của nó.</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>READ-TABLE-DISCIPLINE</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>DA VAO</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>rule vận hành · không code</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>L-51-AMD-FIELD</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>batch_lessons_202609 · L-51 amendment · Alpha klines taker mirror (GUA/TRIA)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>L-51 amendment TẦNG FIELD (bless từ ANALYSIS 2026-09-01): Kỷ luật identity áp cả tầng field — field/cột tồn tại ≠ field có nghĩa. Trước khi tiêu thụ field từ venue/API: verify semantics native (không mirror/placeholder/echo — test bất-biến kiểu k[9]≡k[5]). Án lệ: Alpha klines taker mirror volume → taker = ABSTAIN-STRUCTURAL (GUA/TRIA). Hệ quả đã ký từ trước: taker-native-or-ABSTAIN (spot venue rule 19/08) — amendment này cho nó số nhà.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>IDENTITY-FIELD-AMENDMENT</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>DA VAO</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>grep k[9] rải rác reports/handover · playbook §IX ⑩-B3-TAKER k[10]/k[7] canonical · đóng câu (d) verify-map Phần B</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>L-72</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>lessons_duoi_batch_20260901 (chuyến-5 · kế thừa &amp; đóng đuôi-batch-3 01/09) · TOOL-REVIVAL</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Dụng cụ của một rule đã CLOSED... chặn tay (01/09).</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>TOOL-DISCIPLINE</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>DA VAO</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>H4-detector CLOSED-BY-PRINCIPLE-20260901 (yaml goi_nhe.h4) · candidate ANALYSIS bless verbatim</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>L-73</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>lessons_duoi_batch_20260901 (chuyến-5 · kế thừa &amp; đóng đuôi-batch-3 01/09) · CEX-LIST one-source · án 02/09</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Holder-endpoint (/tgm/holders) = CASE-SUPPORT THEO LỆNH OPERATOR ĐÍCH DANH duy nhất — không máy nào tự tiêu thụ làm signal (H4-detector CLOSED vĩnh viễn). Mọi bảng holder in cột is_cex từ MỘT nguồn `data/ref/cex_addresses_bsc.txt` (md5 0983fb5f8a190872ac2b904798b3cbf7 · reconcile chốt 02/09 · Option A giữ file .txt hiện hành) · cấm list ad-hoc.</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>CEX-LIST-DISCIPLINE</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>DA VAO</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>yaml goi_nhe.survey_holder (ce7da8c6) wire is_cex · probe B2 Gate.io relabel verified · pre-commit hook (chờ ANALYSIS bless format)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>L-74</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>lessons_duoi_batch_20260901 (chuyến-5 · kế thừa &amp; đóng đuôi-batch-3 01/09) · VIEW-AUTO-REGEN · án case_state_map 6.2d</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>(a) tự regen ≤24h · (b) header source_md5+generated_at · (c) consumer đối chiếu → [VIEW-STALE age=Xd] · án lệ case_state_map 6.2d.</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>VIEW-DISCIPLINE</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>DA VAO</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>(a) Windows Task Scheduler regen_case_state_map daily 08:00 VN · (b) HTML comment header inject vào case_state_map.md · (c) scripts/lib/view_stale_check.py + run_phase_tag.py consumer wired · VPS self-test [VIEW-FRESH]</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>L-75</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>lessons_duoi_batch_20260901 (chuyến-5 · kế thừa &amp; đóng đuôi-batch-3 01/09) · MIGRATION-MORNING-PROTOCOL · thành luật</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>MIGRATION-MORNING-PROTOCOL (drop -draft suffix per operator 02/09 · thành luật): audit-kép forensics (evidence trước · verdict sau) · ba-tầng-vá kết dính (mtime + stderr + getter-fail-loud) · snapshot ledger contract-document mọi anomaly · cấm skip verdict khi evidence dở dang · migration nào cũng cần forensics trước khi khép án.</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>MIGRATION-DISCIPLINE</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>DA VAO</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Ba-tầng-vá 31/08 (B2 mtime · B3/B4 stderr · L-51 getter) · L-74 VIEW-AUTO-REGEN 01/09 · snapshot ledger 02/09 · audit-kép AUDIT-KÉP-A/B 02/09</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>L-76</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>lessons_duoi_batch_20260901 (chuyến-5 · kế thừa &amp; đóng đuôi-batch-3 01/09) · SMOKE-KHÔNG-ĐƯỢC-VIẾT-PROD · án CSV 09-01 LOST</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>SMOKE-KHÔNG-ĐƯỢC-VIẾT-PROD (verbatim): smoke ghi prod-path = phẫu-thuật-không-chữ-ký. Án lệ: CSV 09-01 LOST (md5-pre≡post lộ vụ · byte gốc mất vì smoke verification overwrite trước state-surgery chữ ký). Enforcement: default = SANDBOX (env-less) · SIGNED mode explicit qua GOM_H_MODE=SIGNED · banner in mode mỗi run · post-smoke assert md5 prod-scratch unchanged (lệch = [N/A-ERROR:SMOKE-WROTE-PROD]).</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>SMOKE-DISCIPLINE</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>DA VAO</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>scripts/gom_h_daily.py FLIP default=SANDBOX + GOM_H_MODE=SIGNED explicit · scripts/lib/assert_prod_scratch_unchanged.py --snapshot|--verify · cron VPS explicit GOM_H_MODE=SIGNED · verified end-to-end 02/09</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>L-77</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>lessons_duoi_batch_20260907 (đuôi L-77/L-78 · ANALYSIS niêm) · PORT-PARITY</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>PORT-PARITY: mọi PORT (chuyển 1 renderer/sender/detector từ máy A sang máy B) PHẢI kèm golden-master diff trước khi B thay A. Diff bắt buộc: {snapshot cố định} + {A render capture} + {B render capture} + {bảng 4 cột deviation} + {phân loại per-dòng SIGNED (cite chữ) vs DRIFT (revert to A verbatim)}. "Copy logic" mà KHÔNG có diff = mere claim. Án lệ (VPS-digest-drift 4-điểm 01-02/09): digest_daily_vps.py port từ Windows alerts.send_exchange_digest (a) đảo filter OR→AND (bug logic silent · Windows OR pct_pass|usd_pass · VPS đang AND); (b) mất bal-column (signal quan trọng); (c) mất 2-block 📥/📤 layout với section header + rank reset; (d) mất count-line direction '(X lên / Y rời)' + '⚠ K fail'. Deviation-ký S6/DEV-CAP-01: S6 (plain-text digest) SUPERSEDED bởi PARITY-FIX 02/09 (parse_mode=HTML + &lt;pre&gt; + html.escape); DEV-CAP-01 (🏦 caption-drop 'áp lực bán'/'đang gom') vào §E.3 v1.1 (master ≡ Σ khối-cũ ∪ {DEV-CAP-01}), golden_A_exch REV kèm diff dưới chữ v1.1. Fixture md5 pin (L-67 family): golden_A_fresh df772d84 · golden_A_exch 868edfd8 · REV ac34e1b7 + .diff 88a0d2c1.</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>PORT-DISCIPLINE</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>DA VAO</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>docs/proposals/master_report_spec_v1_1_20260903.md §E.3 · tests/fixtures/parity/{golden_A_*,MANIFEST.md,FIXTURE_MASTER_MD5.md} · tests/parity/run_parity_check_20260831.py (CUT_OVER flag · HAI-GOLDEN SCOPE) · docs/handover/l77_candidate_port_parity_20260902.md · digest_daily_vps.py post-fix 4bed9dbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>L-78</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>lessons_duoi_batch_20260907 (đuôi L-77/L-78 · ANALYSIS niêm) · SEAL-KHÔNG-PHẢI-GƯƠNG bản BA-VẾ (ANALYSIS cuối)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>SEAL-KHÔNG-PHẢI-GƯƠNG · bản BA-VẾ (ANALYSIS chốt-cuối):
+(1) HAI VẾ SAI PHẢI ĐỘC LẬP — không thể sai cùng lúc bởi cùng nguyên nhân.
+(2) KHÔNG CÙNG-MỘT-OBJECT — hai vế đọc từ nguồn khác nhau, không chỉ khác đường code đọc (cùng in-memory object đọc bằng 2 fn khác nhau = vẫn cùng-object · KHÔNG PHẢI ĐỘC LẬP).
+(3) ĐẲNG THỨC THEO BẤT-BIẾN, KHÔNG KỊCH BẢN — assert n1 ≡ n2 theo invariant của hệ, không tự chọn context để "đúng có điều kiện".
+Án lệ kép: (a) counter≡counter 03/09 (sidecar assert_equal DEPRECATED · cả 2 vế = in-memory counter của cùng SidecarEmitter · same-object · KHÔNG L-78 compliant · phát hiện qua rewrite → assert_equal_independent vế-2 = re-read JSONL); (b) posthoc same-object 07/09 (extractor emit + JSONL re-read · cả 2 đều post-hoc parse từ cùng text · vẫn same-object · fix rev2 = vế-2 phải là renderer's SELF-DECLARED count trong log). CHUẨN NỘP: sabotage-proof CÓ NHÁNH FAIL — SANDBOX test phải chứng cả happy path VÀ &gt;=3 fail path (file tamper delete row / caller passes wrong count / rogue append) trước khi SCP prod. Nếu không chứng nhánh FAIL = assert chưa niêm.</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>SEAL-DISCIPLINE</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>DA VAO</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>scripts/lib/sidecar_emitter.py (assert_equal_independent · deprecates assert_equal) · scripts/sidecar_extract_post_hoc.py rev2 (target-block anchoring · L-78 self-declared vế-2) · tests/harness/assert_p11_sup_note_parity.py (2-path CSV re-read + fresh scan) · docs/handover/posthoc_expiry_ticket_20260907.md · docs/handover/p11_sup_note_parity_20260903.md · SANDBOX prove: _probe_assert_2path_prove_20260903.py (4/4 · 1 happy + 3 FAIL paths)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>L-79</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>BLOCKER-BỊA + DEMO-RUỘT</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>REV10-e171c341</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Placeholder PENDING-&lt;x&gt; khi source artifact sẵn = bịa. Demo-ruột: preview phải kiểm ruột trước trình.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>REV10-APPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>L-78-append</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>vế-tồn-tại (EMPTY-GUARD)</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>REV10-e171c341</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Bốn-vế: (1) độc-lập · (2) không cùng-object · (3) đẳng-thức bất-biến · (4) vế-tồn-tại (empty-guard).</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>REV10-APPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>án-lệ-✓-suy</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>phái sinh L-79</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>REV10-e171c341</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Nhãn chưa seal → in [UNVERIFIED] · CẤM ✓ suy.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>REV10-APPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>§B-v1.8</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>cộng dồn V3.1-V3.5i</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>REV10-e171c341</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>SỔ-ĂN-SỰ-KIỆN · SENT-anchor · FRESH-Δ-only · EPISODE×COVERAGE · WATERFALL · strict-139/[NGOÀI-SỔ]/[≥3×]-đề-cử · LATTICE max-severity · STICKY-đích-danh · first-seed-any-axis · READ-BACK VERIFY · anchor-139.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>REV10-APPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>p14-DẢI-KÉP</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>PROVISIONAL control-27/09</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>REV10-e171c341</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>chân-a n_PRE∈[4,6] · chân-b n_treo≤15 ∧ coverage-sạch(all ≥15/31) · sort dải-a=star_birth DESC · sort dải-b=last-signal ASC · coverage thủng → CAVEAT án-ở-ống.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>REV10-APPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>p15-semantics</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>UNIVERSE-BOUND FAIL-ENGINE with NAMES</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>REV10-e171c341</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>n_unique mọi trục ≤ |universe|=139 · vi phạm = FAIL-ENGINE treo verdict · in ĐÍCH DANH oob syms · CẤM silent-drop · universe cite = file+md5.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>REV10-APPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>PIN-TUYỂN-DỤNG</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>14 pin distinct · 17 sabotage rows</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>REV10-e171c341</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Mỗi pin ≥1 mutate thật · 4-field log (pin·mutate·verdict·revert-sha) · nhánh luật-chết viết lại trước · p2-p6 FAIL-VACUOUS · p15 FAIL-ENGINE-NAMED · sweep prefix-match.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>REV10-APPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>KHÓA-ĐÍCH-DANH</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>sticky tag in-message</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>REV10-e171c341</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Sticky-source chỉ match {🔴-block · WASH-CRASH · S4/S5} · CẤM ¹-generic · tag `STICKY-XẢ vì &lt;src&gt;-&lt;DD/MM&gt;` in trên dòng ⭐.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>REV10-APPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>WL-án-lệ</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>18≡18 verbatim</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>REV10-e171c341</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>18≡18 đối-chứng-hai-nguồn · 44-unique · List-B[23,44]avg34.6 · thác 157→16 · thay vĩnh viễn mọi trích tiền-REV4.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>REV10-APPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>star_birth-def</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>trục-thứ-hai tới</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>REV10-e171c341</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>star_birth(token) := min{d : |{trục có event ≤ d}| ≥ 2}.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>REV10-APPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>⭐-01-entry#1</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>COLLECT bảng-chấm-⭐</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>REV10-e171c341</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>COLLECT direction=POST-DUMP · ret=-40.0% · dd=-53.6% · sổ chấm: 'máy fire trước sóng (TP-recall) · ledger gán chiều sai 4 ngày (FP-direction)'.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>REV10-APPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>L-80-DRAFT</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>regex block-scoped enforcement</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>REV10-e171c341</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>'Regex đọc log đa-target PHẢI block-scoped (anchor target → next-target/EOF); DOTALL-span = phantom-đếm.' Án lệ kép: forensic-25-phantom 07/09 · extractor-watchlist 62≠30. DRAFT-KHÔNG-KÍCH-HOẠT.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>REV10-APPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>LABEL-CLAIMS-LINT</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>án lệ #2 + #2b</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>REV10-e171c341</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Grep nhãn CLAIM {sorted·sort:·✓·checked·verified·OK·PASS·đã-*} · hợp lệ khi bán kính k=5 có phép-kiểm hoặc cite [per &lt;seal-id&gt;]. Án lệ #2: '5/5 WIRED ✅' không biên lai orphan. Án lệ #2b: claim-✅-giả toàn phần (watchlist wire 0 dump_as_sent).</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>REV10-APPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>SỔ-ĐỌC-ENFORCEMENT</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>regex đa-target block-scoped</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>REV10-e171c341</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Regex đọc log đa-target = block-scoped. Fix wired _wl_sent_by_target.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>REV10-APPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>DOS-PACKAGE</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ghế 27/09</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>REV10-e171c341</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Câu kiến trúc: 'exposure-declared-theo-thế-hệ tầng universe — đổi mẫu số tại ranh thế hệ'. DOS 4×/30d ĐỀ-CỬ-UNIVERSE bất động 27/09. BEAT/ONE/B đếm tiếp.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>REV10-APPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>[SENT]-marker-chuẩn</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>L-59 áp mọi sender</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>REV10-e171c341</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Mọi sender in `[SENT] &lt;kênh&gt; ok=&lt;bool&gt; HTTP &lt;code&gt; hash=&lt;h&gt;`. Wired: gom_daily · phase_map · watchlist.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>REV10-APPLY</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -10,6 +10,7 @@
     <sheet name="LESSONS" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="MM_BOOK" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="PHAN_VAI" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="CASES" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1741,7 +1742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:R121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5300,6 +5301,1097 @@
       <c r="I101" t="inlineStr">
         <is>
           <t>REV10-APPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="102"/>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>LR_id</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>ve</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>loai</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>support_n</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>counter_n</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>cases_support</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>cases_counter</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>cases_not_applicable</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>cases_true_negative</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>cases_pending</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>gate_binding</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>evidence_class</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>thresholds_signed</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>signed_by</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>signed_date</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>last_regrade</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>changelog</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>LR-01b</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>pos_r ≥[3] ∧ pin ≥[7d] ∧ |ΔOI 14d| ≤[15%] ∧ px ≤ đáy dải 30d → ×3/120d</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>A-stealth</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>2</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>BANK:2026-07-19:7e520f40, TUT:2026-08-02:4ab482bc</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>AKE:2026-09-10:92fa9c56, BTW:2026-09-10:ffe6b6de, BTR:2026-09-10:c988194e, 龙虾:2026-09-10:2b727853</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>HYPOTHESIS</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>2026-09-10 · seed · T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>LR-04</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>vol ≥×[8] med14 ∧ ret về ±[10%] nền ≤3d ∧ ≤[45]d trước D0 (bait-probe)</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11</v>
+      </c>
+      <c r="E105" t="n">
+        <v>2</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>BANK:2026-09-10:7e520f40, TUT:2026-09-10:4ab482bc, AKE:2026-09-10:92fa9c56, BTW:2026-09-10:ffe6b6de, BTR:2026-09-10:c988194e, CAP:2026-09-10:2695bc3f, ON:2026-09-10:4e0e3a7a, HEMI:2026-09-10:4238441f, BULLA:2026-09-10:deb0b268, 龙虾:2026-09-10:2b727853, UAI:2026-09-10:af767473</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>CYS:2026-09-10:af073e64, PROM:2026-09-10:b50b1f68</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>RETIRED</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>2026-09-10 · seed · T1 · 2026-09-11 · CANDIDATE→RETIRED · counter_n=2≥2</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>LR-05</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>taker_buy &lt;[55%] xuyên markup (≤1 ngày eve)</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>13</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>AKE:2026-09-10:92fa9c56, TUT:2026-09-10:4ab482bc, BANK:2026-09-10:7e520f40, BTW:2026-09-10:ffe6b6de, BTR:2026-09-10:c988194e, CAP:2026-09-10:2695bc3f, ON:2026-09-10:4e0e3a7a, HEMI:2026-09-10:4238441f, BULLA:2026-09-10:deb0b268, 龙虾:2026-09-10:2b727853, UAI:2026-09-10:af767473, CYS:2026-09-10:af073e64, PROM:2026-09-10:b50b1f68</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>RULE-XÁC-NHẬN</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>descriptive:55</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>Tiên</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>2026-09-10 · seed · T1 · Tiên ký 10/09</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>LR-06</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>pos_r ↓ ≥25% ∧ OI ↑ ∧ gLSR ↓ = crowd-short-nạp (fuel), không phải MM exit</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>A/D</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>TUT:2026-08-02:4ab482bc</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>BANK:2026-07-19:7e520f40</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>HYPOTHESIS</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>2026-09-10 · seed · T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>LR-07</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>nạp ≥[50%]/5d ∧ ret ≤−[30%]/5d ∧ plateau ≥[5]d ∧ acc ≥[2] ∧ div_avg3 TĂNG = STAGING (làm giá)</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>B/C</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>2</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>AKE:2026-09-10:92fa9c56, BTR:2026-09-10:c988194e</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>BANK:2026-07-20:7e520f40</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>HYPOTHESIS</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>2026-09-10 · seed · T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>LR-08</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>GOM-E un-hedge ∧ kho ≥50%/5d ∧ px −30% → lead [8-9]d</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>AKE:2026-09-10:92fa9c56</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>HYPOTHESIS</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>2026-09-10 · seed · T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>LR-09</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>G3(b) vế "OI-build" sai; seat-lift = pos_ramp trên OI phẳng; div TĂNG từ ≤0.5</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>B/C</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>3</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>AKE:2026-09-10:92fa9c56, CYS:2026-09-10:af073e64, PROM:2026-09-10:b50b1f68</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>CANDIDATE</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>2026-09-10 · seed · T1 (→ AMD-05 B3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>LR-10</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>acc_r sập ≥[40-50%]/≤3d quanh ignition = xác nhận muộn (không phân biệt E)</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>13</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>AKE:2026-09-10:92fa9c56, TUT:2026-09-10:4ab482bc, BANK:2026-09-10:7e520f40, BTW:2026-09-10:ffe6b6de, BTR:2026-09-10:c988194e, CAP:2026-09-10:2695bc3f, ON:2026-09-10:4e0e3a7a, HEMI:2026-09-10:4238441f, BULLA:2026-09-10:deb0b268, 龙虾:2026-09-10:2b727853, UAI:2026-09-10:af767473, CYS:2026-09-10:af073e64, PROM:2026-09-10:b50b1f68</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>RULE-XÁC-NHẬN</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>descriptive:40-50</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Tiên</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>2026-09-10 · seed · T1 · Tiên ký 10/09</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>LR-11</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>decay/S5 SUPPRESSED cần TTL hoặc vế đảo (OI +[40%]/14d trên giá phẳng)</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>C/D</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>BTW:2026-09-10:ffe6b6de</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>HYPOTHESIS</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>2026-09-10 · seed · T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>LR-12</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>kho RÚT trước pump ở loài A; kho NẠP ở loài B/C/D — đọc theo loài</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>A vs B/C/D</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>6</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>CYS:2026-09-10:af073e64, 龙虾:2026-09-10:2b727853, UAI:2026-09-10:af767473, AKE:2026-09-10:92fa9c56, HEMI:2026-09-10:4238441f, BTR:2026-09-10:c988194e</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>BANK:2026-09-10:[CHART-READ], PROM:2026-09-10:[CHART-READ], CAP:2026-09-10:[CHART-READ], ON:2026-09-10:[CHART-READ]</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>CANDIDATE</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>2026-09-10 · seed · T1 · 4 ảnh CHART-READ trong cases_pending (BANK/PROM/CAP/ON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>LR-13</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>unhedge-event = div_avg3 vượt 0.5→[0.7] ≤3d ∧ Δacc ≤−[15%] ∧ |Δpos| ≤[10%] (crowd rời); Δpos ≥+[20%] = whale đổi ghế (bẫy)</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>3</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>BTR:2026-09-10:c988194e, BULLA:2026-09-10:deb0b268, UAI:2026-09-10:af767473</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>SOPH:2026-06-27:344cf3c8, SOPH:2026-07-12:344cf3c8, SOPH:2026-08-08:344cf3c8</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>CANDIDATE</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>2026-09-10 · seed · T1 · counter 3→0 SOPH×3→TN</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>LR-14</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>deposit-in-pump không kết thúc sóng nếu pos_r hồi ≥ trước-flush ≤3d</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>HEMI:2026-09-10:4238441f</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>BANK:2026-09-10:7e520f40, BTR:2026-09-10:c988194e, ON:2026-09-10:4e0e3a7a, 龙虾:2026-09-10:2b727853</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>HYPOTHESIS</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>2026-09-10 · seed · T1 · counter 4→0 BANK/BTR/ON/龙虾→TN</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>LR-15</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>nến ≥+[35%] ∧ spot/perp ≤[1.2%] ∧ không nến ≥+[10%] trong ≤3d ∧ crowd đảo long D+2-3 = rụng</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>2</v>
+      </c>
+      <c r="E116" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>APR:2026-09-10:2f0918b6, SOPH:2026-09-10:344cf3c8</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>HEMI:2026-09-10:4238441f</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>HYPOTHESIS</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>2026-09-10 · seed · T1 (R7 in 3 vế, không verdict) · 2026-09-11 · CANDIDATE→HYPOTHESIS · support_n=2&lt;3</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>LR-16</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>GOM-A A1 bắn sau khi crowd bị rửa (div nở do acc sập), không phải khi whale gom</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>3</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>HEMI:2026-09-10:4238441f, BULLA:2026-09-10:deb0b268, UAI:2026-09-10:af767473</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>PROM:2026-09-10:b50b1f68</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>CANDIDATE</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>2026-09-10 · seed · T1 · counter 1→0 PROM→NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>LR-17</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>OI trước ignition: giảm ở loài A (CYS −40%, PROM −25%, UAI −27%); build ở loài D (BTW +54%, 龙虾 +64%); phẳng còn lại — OI không phải luật chung</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>A vs D</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>5</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>CYS:2026-09-10:af073e64, PROM:2026-09-10:b50b1f68, UAI:2026-09-10:af767473, BTW:2026-09-10:ffe6b6de, 龙虾:2026-09-10:2b727853</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>CANDIDATE</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>2026-09-10 · seed · T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>LR-18</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Nansen bal_date trễ [1-3]d: lead từ kho phải trừ; replay không thay findings khi coverage mù</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>5</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>AKE:2026-09-10:92fa9c56, HEMI:2026-09-10:4238441f, BANK:2026-09-10:7e520f40, ON:2026-09-10:4e0e3a7a, APR:2026-09-10:2f0918b6</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>CANDIDATE</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>2026-09-10 · seed · T1 (operator explicit: CANDIDATE, không RULE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>LR-20</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>hedge-struct ≥[30]d không unhedge-event = CHRONIC (FP); List-A cần TTL</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>SOPH:2026-09-10:344cf3c8</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>HYPOTHESIS</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>2026-09-10 · seed · T1 (→ A3/B4) · 2026-09-11 · CANDIDATE→HYPOTHESIS · support_n=1&lt;3</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>L-28 am.1</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>whales_config căn cước bằng giá contract</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>MIGRATION-CLASSIFIER-28-09</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>nguồn ngoài neo căn cước = khớp giá CỦA ĐỊA CHỈ với perp (≤[5×]); giá theo symbol (spot/Alpha-symbol) là sanity-circle, không dùng cho căn cước/DEAD; symbol, Alpha entry, CoinGecko chỉ là ứng viên. Ca: ARX · STAR · BOB · ONE (trùng contract với CROSS) · PLAY · TAC.</t>
         </is>
       </c>
     </row>
@@ -5640,4 +6732,1377 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>display_token</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>path</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>case_xlsx_md5_after</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>addendum_count</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ledger_count</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>loài</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>trạng_thái</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>added_at_utc</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>kr_share_14d_pct</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>kr_led</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BANK</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BANK</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>docs/case_files/BANK/</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>b550820d70cc0eb46b3d1defea398409</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>proven·hedge</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>proven</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-09-10T10:11:07.862843+00:00</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>39.2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>docs/case_files/TUT/</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>8580030a491520526b70937c401934ec</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>proven</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>proven</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-09-10T10:11:07.862843+00:00</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>N/A-NOT-IN-KR-SWEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AKE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AKE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>docs/case_files/AKE/</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8b86051c70009442c354238bebca8e8b</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>proven·hedge</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>proven</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-09-10T10:11:07.862843+00:00</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>N/A-NOT-IN-KR-SWEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BTW</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BTW</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>docs/case_files/BTW/</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>be21051483eaa5b01875d82844ef6b09</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>proven</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>proven</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-09-10T10:11:07.862843+00:00</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>N/A-NOT-IN-KR-SWEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CYS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CYS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>docs/case_files/CYS/</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>5603f3dbcfc598cc4865e3ff5991c8bc</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>proven</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>proven</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-09-10T10:11:07.862843+00:00</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>73.29000000000001</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>KR-DẪN</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BTR</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BTR</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>docs/case_files/BTR/</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>7dc7191c1854e7c5649e92af1ee13fdb</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>đối chứng</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>đối chứng</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-09-10T10:11:07.862843+00:00</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>KR-DẪN</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAP</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CAP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>docs/case_files/CAP/</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>c5ecf59044d31002f77e825adaf58300</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-09-10T10:11:07.862843+00:00</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>55.67</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>KR-DẪN</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>docs/case_files/ON/</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>c550d14ab2e282e096fee1bc66d9cfb2</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>proven·hedge</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>proven</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-09-10T10:11:07.862843+00:00</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>N/A-NOT-IN-KR-SWEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>APR</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>APR</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>docs/case_files/APR/</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0750f1df6c735590825e632e22bc03ec</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>đối chứng·1-cột</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>đối chứng</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-09-10T10:11:07.862843+00:00</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>N/A-NOT-IN-KR-SWEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HEMI</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HEMI</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>docs/case_files/HEMI/</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ff0e2eb5e004b48b02e1973fe3f31bb7</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>proven·hedge</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>proven</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-09-10T10:11:07.862843+00:00</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>37.14</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BULLA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BULLA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>docs/case_files/BULLA/</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>c0b0f50746d16504327ef986110eca86</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>proven·sống·2-sóng</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>sống (sóng-2 mở)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-09-10T10:11:07.862843+00:00</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>N/A-NOT-IN-KR-SWEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PROM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PROM</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>docs/case_files/PROM/</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>820fe247aae802cdabefb83f1687150e</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>đối chứng</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>đối chứng</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-09-10T10:11:07.862843+00:00</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>31.95</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LOBSTER</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>龙虾</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>docs/case_files/LOBSTER/</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1566884da03567be5d78e9783dd6c49a</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>proven·kho90%</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>proven</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-09-10T10:11:07.862843+00:00</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>N/A-NOT-IN-KR-SWEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>UAI</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>UAI</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>docs/case_files/UAI/</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4fa8599e6fa2c238d275ef5cc701861a</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>proven·hedge</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>proven</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-09-10T10:11:07.862843+00:00</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>N/A-NOT-IN-KR-SWEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SOPH</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SOPH</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>docs/case_files/SOPH/</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>cf7c8c78b9eff091993a2a635f13e048</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>đối chứng·1-cột</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>đối chứng</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-09-10T10:11:07.862843+00:00</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>83.19</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>KR-DẪN</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LIGHT</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LIGHT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>docs/case_files/LIGHT/</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4bfcca85346edb0822fd36291af19501</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SỐNG [KHUÔN-draft] · GRIND-DEPOSIT</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>SỐNG</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-09-11T08:05:46Z</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>N/A-NOT-IN-KR-SWEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BROCCOLIF3B</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BROCCOLIF3B</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>docs/case_files/BROCCOLIF3B/</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>82dd9b10244f0f9356811786267899ec</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SỐNG [KHUÔN-draft] · meme 1Y · Nansen NOT-TRACKED</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>SỐNG</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-09-11T08:33:44Z</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>N/A-NOT-IN-KR-SWEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>docs/case_files/AT/</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>7e2b5e3553942bd1910001e6eb563cc4</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SỐNG [KHUÔN-draft] · 2M window</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>SỐNG</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-09-11T08:48:48Z</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>N/A-NOT-IN-KR-SWEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BASED</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BASED</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>docs/case_files/BASED/</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>9be1966928a0d415f97d7b40acc7b673</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SỐNG [KHUÔN-draft] · census H1 26/07 MED</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>SỐNG</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-09-11T09:05:55Z</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>49.12</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MARSCOIN</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MARSCOIN</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>docs/case_files/MARSCOIN/</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>eb47a65c80958f776d7976fd82b7670c</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>SỐNG [KHUÔN-draft] · perp 9d · Nansen NOT-TRACKED · meme 100%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>SỐNG</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-09-11T09:30:27Z</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>N/A-NOT-IN-KR-SWEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>HYPER</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HYPER</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>docs/case_files/HYPER/</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>755ee510a52db522bf2d03b30ead913e</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>SỐNG [KHUÔN-draft] · Hyperlane BSC · Alpha delisted · kho TRACKED</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>SỐNG</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-09-11T14:34:57Z</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>38.95</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>docs/case_files/RED/</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>047c6d1edd02c779080470a53025bfde</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>SỐNG [KHUÔN-draft] · perp+spot · NO Alpha · Nansen NOT-TRACKED</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>SỐNG</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-09-11T14:50:04Z</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>47.9</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MITO</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MITO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>docs/case_files/MITO/</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>e64fb345b398cafcb193eb669204c207</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>SỐNG [KHUÔN-draft] · XẢ-WATCH · D7=3/8 · fork A/B/C</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>SỐNG</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-09-11T22:55:39Z</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>N/A-NOT-IN-KR-SWEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>WTMLL</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>我踏马来了</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>docs/case_files/WTMLL/</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>abd9050a3b01c85bfd654fe45b99569b</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>SỐNG [KHUÔN-draft] · Chinese-family meme · Nansen TRACKED</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>SỐNG</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-09-12T14:20:43Z</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>N/A-NOT-IN-KR-SWEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ARX</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ARX</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>docs/case_files/ARX/</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>b6f7d445b8a8bc91a41c8f744a4bdba0</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>SỐNG [KHUÔN-draft] · Arcium · Nansen NOT-TRACKED · spot N/A</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>SỐNG</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-09-12T15:02:44Z</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>72.54000000000001</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>KR-DẪN</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>POWER</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>POWER</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>docs/case_files/POWER/</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>63ef70aa024d796b65dc621d4c570ce7</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>SỐNG [KHUÔN-draft] · Power Protocol · cover-event 02/09</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>SỐNG</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-09-13T08:04:30Z</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>N/A-NOT-IN-KR-SWEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>LSK</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LSK</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>docs/case_files/LSK/</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>8a65c3e6798db9fdcdc0fa70eb712b1b</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>SỐNG [KHUÔN-draft] · Lisk L1/L2 · spot TRADING · B-top 08-13→08-17</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>SỐNG</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:12:27Z</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>71.54000000000001</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>KR-DẪN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/case_files/CASE_INDEX.xlsx
+++ b/docs/case_files/CASE_INDEX.xlsx
@@ -1742,7 +1742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R121"/>
+  <dimension ref="A1:R123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>RULE-XÁC-NHẬN</t>
+          <t>PROMOTED→L-81</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-09-10 · seed · T1 · Tiên ký 10/09</t>
+          <t>2026-09-10 · seed · T1 · Tiên ký 10/09 · 2026-09-28 promoted</t>
         </is>
       </c>
     </row>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>RULE-XÁC-NHẬN</t>
+          <t>PROMOTED→L-82</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-09-10 · seed · T1 · Tiên ký 10/09</t>
+          <t>2026-09-10 · seed · T1 · Tiên ký 10/09 · 2026-09-28 promoted</t>
         </is>
       </c>
     </row>
@@ -6392,6 +6392,50 @@
       <c r="D121" t="inlineStr">
         <is>
           <t>nguồn ngoài neo căn cước = khớp giá CỦA ĐỊA CHỈ với perp (≤[5×]); giá theo symbol (spot/Alpha-symbol) là sanity-circle, không dùng cho căn cước/DEAD; symbol, Alpha entry, CoinGecko chỉ là ứng viên. Ca: ARX · STAR · BOB · ONE (trùng contract với CROSS) · PLAY · TAC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>L-81</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>taker_buy pin xuyên markup</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>PROMOTE-LR-05-28-09</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>taker_buy &lt;[55%] xuyên markup (≤1 ngày eve) · ngưỡng descriptive:55 · evidence_class=E2 · support_n=13 · counter_n=0 · gate_binding=N · promoted from LR-05 (gieo 10/09 · bada4e50) · ký chat Tiến 28/09</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>L-82</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>acc_r sập quanh ignition = xác nhận muộn</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>PROMOTE-LR-10-28-09</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>acc_r sập ≥[40-50%]/≤3d quanh ignition = xác nhận muộn (không phân biệt E) · ngưỡng descriptive:40-50 · evidence_class=E2 · support_n=13 · counter_n=0 · gate_binding=N · promoted from LR-10 (gieo 10/09 · bada4e50) · ký chat Tiến 28/09</t>
         </is>
       </c>
     </row>
